--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DCB747-1E0E-437E-94A8-9CC20FFB2E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54422EBD-2E66-4DCE-8515-944C7678EB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="740">
   <si>
     <t>Prénom</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Date de création</t>
   </si>
   <si>
-    <t xml:space="preserve">Ville de création </t>
+    <t>Lieu de conservation</t>
   </si>
   <si>
     <t>Lieu précis de conservation</t>
@@ -142,6 +142,15 @@
     <t>Marbre</t>
   </si>
   <si>
+    <t>133 cm</t>
+  </si>
+  <si>
+    <t>125 cm</t>
+  </si>
+  <si>
+    <t>95 cm</t>
+  </si>
+  <si>
     <t>1884</t>
   </si>
   <si>
@@ -181,6 +190,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b4/Emancipation_memorial_MRD.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
+    <t>366 cm (statue) 366 cm (piédestal)</t>
+  </si>
+  <si>
     <t>américaine</t>
   </si>
   <si>
@@ -211,6 +223,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c4/La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg/1920px-La_D%C3%A9fense_de_Paris_%40_Parvis_%40_La_D%C3%A9fense_%40_Paris_%2834342635104%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>550 cm</t>
+  </si>
+  <si>
     <t>française</t>
   </si>
   <si>
@@ -256,6 +271,12 @@
     <t>Grès rose</t>
   </si>
   <si>
+    <t>1056 cm</t>
+  </si>
+  <si>
+    <t>1906 cm</t>
+  </si>
+  <si>
     <t>1886</t>
   </si>
   <si>
@@ -271,6 +292,9 @@
     <t>Cuivre repoussé (structure Eiffel)</t>
   </si>
   <si>
+    <t>4600 cm (statue) 4700 cm (piédestal)</t>
+  </si>
+  <si>
     <t>Lorenzo</t>
   </si>
   <si>
@@ -364,6 +388,9 @@
     <t>Bronze et marbre</t>
   </si>
   <si>
+    <t>295 cm (statue) 200 cm (piédestal et allégories)</t>
+  </si>
+  <si>
     <t>allemande</t>
   </si>
   <si>
@@ -379,6 +406,12 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Neptunbrunnen_Berlin_2.jpg/1280px-Neptunbrunnen_Berlin_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>1000 cm</t>
+  </si>
+  <si>
+    <t>1800 cm (diamètre)</t>
+  </si>
+  <si>
     <t>François Joseph</t>
   </si>
   <si>
@@ -424,420 +457,480 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg/1280px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Au_But_%28Alfred_Boucher%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
+    <t>100 cm environ</t>
+  </si>
+  <si>
+    <t>146 cm environ</t>
+  </si>
+  <si>
+    <t>79cm environ</t>
+  </si>
+  <si>
+    <t>1890</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Musée des Beaux-Arts</t>
+  </si>
+  <si>
+    <t>"A la terre"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/A_la_terre_Boucher_MBA_Rennes.jpg/1920px-A_la_terre_Boucher_MBA_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>40 cm environ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 cm environ </t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>CANOVA</t>
+  </si>
+  <si>
+    <t>1757</t>
+  </si>
+  <si>
+    <t>1822</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>Vienne</t>
+  </si>
+  <si>
+    <t>Kunsthistorischen Museum</t>
+  </si>
+  <si>
+    <t>"Thésée et le Centaure"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Theseus_and_Centaur_by_Antonio_Canova_1.jpg/1280px-Theseus_and_Centaur_by_Antonio_Canova_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>360 cm environ</t>
+  </si>
+  <si>
+    <t>375 cm</t>
+  </si>
+  <si>
+    <t>141 cm</t>
+  </si>
+  <si>
+    <t>Bakewell</t>
+  </si>
+  <si>
+    <t>Chatsworth House</t>
+  </si>
+  <si>
+    <t>"Endymion dormant"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Antonio_Canova%2C_Endymion_%281%29.JPG/1280px-Antonio_Canova%2C_Endymion_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>105 cm environ</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>CARPEAUX</t>
+  </si>
+  <si>
+    <t>1827</t>
+  </si>
+  <si>
+    <t>1857-1861</t>
+  </si>
+  <si>
+    <t>Petit Palais</t>
+  </si>
+  <si>
+    <t>"Ugolin entouré de ses quatre enfants,"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg/960px-Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Plâtre patiné</t>
+  </si>
+  <si>
+    <t>195 cm</t>
+  </si>
+  <si>
+    <t>150 cm</t>
+  </si>
+  <si>
+    <t>110 cm</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG/960px-Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>194 cm</t>
+  </si>
+  <si>
+    <t>148 cm</t>
+  </si>
+  <si>
+    <t>119 cm</t>
+  </si>
+  <si>
+    <t>Metropolitan Museum of Art</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Ugolino_and_His_Sons_MET_DP247545.jpg/960px-Ugolino_and_His_Sons_MET_DP247545.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>197,5 cm</t>
+  </si>
+  <si>
+    <t>149,9cm</t>
+  </si>
+  <si>
+    <t>110,5 cm</t>
+  </si>
+  <si>
+    <t>1869</t>
+  </si>
+  <si>
+    <t>"La Danse (façade de l'Opéra de Paris)"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1874</t>
+  </si>
+  <si>
+    <t>Jardin des Grands Explorateurs (de l'Observatoire)</t>
+  </si>
+  <si>
+    <t>"Fontaine des Quatre-Parties-du-Monde"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=lt</t>
+  </si>
+  <si>
+    <t>Albert-Ernest</t>
+  </si>
+  <si>
+    <t>CARRIER-BELLEUSE</t>
+  </si>
+  <si>
+    <t>1824</t>
+  </si>
+  <si>
+    <t>1887</t>
+  </si>
+  <si>
+    <t>1863</t>
+  </si>
+  <si>
+    <t>"La Bacchante"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>90 cm environ</t>
+  </si>
+  <si>
+    <t>1866</t>
+  </si>
+  <si>
+    <t>"Hébé endormie"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/CB_H%C3%A9b%C3%A9.jpg/960px-CB_H%C3%A9b%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1873</t>
+  </si>
+  <si>
+    <t>Palais Garnier</t>
+  </si>
+  <si>
+    <t>"Une des torchères du grand escalier de l'Opéra de Paris."</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg/960px-Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bronze doré</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>CHANTREY</t>
+  </si>
+  <si>
+    <t>1781</t>
+  </si>
+  <si>
+    <t>1817</t>
+  </si>
+  <si>
+    <t>Cathédrale de Lichfield</t>
+  </si>
+  <si>
+    <t>"Enfants endormis"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/Chantreys_Sleeping_Children.jpg/1280px-Chantreys_Sleeping_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
+    <t>Henri</t>
+  </si>
+  <si>
+    <t>CHAPU</t>
+  </si>
+  <si>
+    <t>1833</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>"Jeanne d’Arc à Domremy"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Henri_Chapu_-_Jeanne_d%27Arc.jpg/960px-Henri_Chapu_-_Jeanne_d%27Arc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>190 cm environ</t>
   </si>
   <si>
-    <t>1890</t>
-  </si>
-  <si>
-    <t>Rennes</t>
-  </si>
-  <si>
-    <t>Musée des Beaux-Arts</t>
-  </si>
-  <si>
-    <t>"A la terre"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/A_la_terre_Boucher_MBA_Rennes.jpg/1920px-A_la_terre_Boucher_MBA_Rennes.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>CANOVA</t>
-  </si>
-  <si>
-    <t>1757</t>
-  </si>
-  <si>
-    <t>1822</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>Vienne</t>
-  </si>
-  <si>
-    <t>Kunsthistorischen Museum</t>
-  </si>
-  <si>
-    <t>"Thésée et le Centaure"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Theseus_and_Centaur_by_Antonio_Canova_1.jpg/1280px-Theseus_and_Centaur_by_Antonio_Canova_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Bakewell</t>
-  </si>
-  <si>
-    <t>Chatsworth House</t>
-  </si>
-  <si>
-    <t>"Endymion dormant"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3f/Antonio_Canova%2C_Endymion_%281%29.JPG/1280px-Antonio_Canova%2C_Endymion_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>105 cm environ</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste</t>
-  </si>
-  <si>
-    <t>CARPEAUX</t>
-  </si>
-  <si>
-    <t>1827</t>
-  </si>
-  <si>
-    <t>1857-1861</t>
-  </si>
-  <si>
-    <t>Petit Palais</t>
-  </si>
-  <si>
-    <t>"Ugolin entouré de ses quatre enfants,"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg/960px-Ugolino_Carpeaux_Petit_Palais_PPSO1573.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>1869</t>
-  </si>
-  <si>
-    <t>"La Danse (façade de l'Opéra de Paris)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG/960px-Jean-Baptiste_Carpeaux_%22La_danse%22_mus%C3%A9e_d%27Orsay_Paris_France.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>Musée Carnavalet</t>
+  </si>
+  <si>
+    <t>"La Jeunesse"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/La_Jeunesse%2C_S3494%2801%29.jpg/960px-La_Jeunesse%2C_S3494%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ernest</t>
+  </si>
+  <si>
+    <t>CHRISTOPHE</t>
+  </si>
+  <si>
+    <t>1892</t>
+  </si>
+  <si>
+    <t>"La Comédie humaine (dit aussi Le Masque)"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Le_Masque-Ernest_Christophe-IMG_8124-black.jpg/1920px-Le_Masque-Ernest_Christophe-IMG_8124-black.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Camille</t>
+  </si>
+  <si>
+    <t>CLAUDEL</t>
+  </si>
+  <si>
+    <t>1864</t>
+  </si>
+  <si>
+    <t>1943</t>
+  </si>
+  <si>
+    <t>1893</t>
+  </si>
+  <si>
+    <t>Musée Rodin</t>
+  </si>
+  <si>
+    <t>"La Valse"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1897</t>
+  </si>
+  <si>
+    <t>"La Vague"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg/960px-Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bronze, marbre et onyx</t>
+  </si>
+  <si>
+    <t>62 cm environ</t>
+  </si>
+  <si>
+    <t>"L'Âge mûr"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Claudel-2014-05.jpg/1280px-Claudel-2014-05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>CLÉSINGER</t>
+  </si>
+  <si>
+    <t>1814</t>
+  </si>
+  <si>
+    <t>1847</t>
+  </si>
+  <si>
+    <t>"La Femme piquée par un serpent"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1848</t>
+  </si>
+  <si>
+    <t>"Bacchante couchée"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Paris_8e_-_Petit_Palais_-_Mus%C3%A9e_des_Beaux-Arts_-_Bacchante_%28Auguste_Cl%C3%A9singer%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Cimetière du Père-Lachaise à Paris</t>
+  </si>
+  <si>
+    <t>"Monument funéraire de Frédéric Chopin"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Chopin_Grave_Grab_Pere_Lachaise.JPG/960px-Chopin_Grave_Grab_Pere_Lachaise.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t>CORDIER</t>
+  </si>
+  <si>
+    <t>1856-1857</t>
+  </si>
+  <si>
+    <t>"Homme du Soudan"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bronze et onyx polychrome</t>
+  </si>
+  <si>
+    <t>Gustave</t>
+  </si>
+  <si>
+    <t>CRAUK</t>
+  </si>
+  <si>
+    <t>Temple de l’Oratoire du Louvre</t>
+  </si>
+  <si>
+    <t>"Statue de Gaspard de Coligny"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Adèle</t>
+  </si>
+  <si>
+    <t>d'AFFRY</t>
+  </si>
+  <si>
+    <t>MARCELLO</t>
+  </si>
+  <si>
+    <t>1836</t>
+  </si>
+  <si>
+    <t>1870</t>
+  </si>
+  <si>
+    <t>Opéra de Paris</t>
+  </si>
+  <si>
+    <t>"Pythie"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/Pythia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>suisse</t>
+  </si>
+  <si>
+    <t>Jules</t>
+  </si>
+  <si>
+    <t>DALOU</t>
+  </si>
+  <si>
+    <t>1838</t>
+  </si>
+  <si>
+    <t>1897-1902</t>
+  </si>
+  <si>
+    <t>"Grand paysan"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Dalou_paysan.jpg/960px-Dalou_paysan.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Place de la Nation</t>
+  </si>
+  <si>
+    <t>"Le Triomphe de la République"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pierre-Jean</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>DAVID D'ANGERS</t>
+  </si>
+  <si>
+    <t>1788</t>
+  </si>
+  <si>
+    <t>1856</t>
+  </si>
+  <si>
+    <t>1837</t>
+  </si>
+  <si>
+    <t>Panthéon</t>
+  </si>
+  <si>
+    <t>"Fronton du Panthéon de Paris"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
     <t>Pierre</t>
   </si>
   <si>
-    <t>1874</t>
-  </si>
-  <si>
-    <t>Jardin des Grands Explorateurs (de l'Observatoire)</t>
-  </si>
-  <si>
-    <t>"Fontaine des Quatre-Parties-du-Monde"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg/1280px-20210307_170507Carpeaux_-_Fr%C3%A9miet_-_Fontaine_des_Quatre-Parties-du-Monde_-_D%C3%A9tail_%28partie_Carpeaux%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=lt</t>
-  </si>
-  <si>
-    <t>Albert-Ernest</t>
-  </si>
-  <si>
-    <t>CARRIER-BELLEUSE</t>
-  </si>
-  <si>
-    <t>1824</t>
-  </si>
-  <si>
-    <t>1887</t>
-  </si>
-  <si>
-    <t>1863</t>
-  </si>
-  <si>
-    <t>"La Bacchante"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9f/Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg/960px-Paris_-_Mus%C3%A9e_d%27Orsay_8503.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>90 cm environ</t>
-  </si>
-  <si>
-    <t>1866</t>
-  </si>
-  <si>
-    <t>"Hébé endormie"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/CB_H%C3%A9b%C3%A9.jpg/960px-CB_H%C3%A9b%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>1873</t>
-  </si>
-  <si>
-    <t>Palais Garnier</t>
-  </si>
-  <si>
-    <t>"Une des torchères du grand escalier de l'Opéra de Paris."</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg/960px-Torch%C3%A8re_du_grand_escalier_du_palais_Garnier_par_Carrier_Belleuse.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Bronze doré</t>
-  </si>
-  <si>
-    <t>Francis</t>
-  </si>
-  <si>
-    <t>CHANTREY</t>
-  </si>
-  <si>
-    <t>1781</t>
-  </si>
-  <si>
-    <t>1817</t>
-  </si>
-  <si>
-    <t>Cathédrale de Lichfield</t>
-  </si>
-  <si>
-    <t>"Enfants endormis"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/19/Chantreys_Sleeping_Children.jpg/1280px-Chantreys_Sleeping_Children.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>anglaise (Royaume-Uni)</t>
-  </si>
-  <si>
-    <t>Henri</t>
-  </si>
-  <si>
-    <t>CHAPU</t>
-  </si>
-  <si>
-    <t>1833</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>"Jeanne d’Arc à Domremy"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Henri_Chapu_-_Jeanne_d%27Arc.jpg/960px-Henri_Chapu_-_Jeanne_d%27Arc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Musée Carnavalet</t>
-  </si>
-  <si>
-    <t>"La Jeunesse"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d5/La_Jeunesse%2C_S3494%2801%29.jpg/960px-La_Jeunesse%2C_S3494%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Ernest</t>
-  </si>
-  <si>
-    <t>CHRISTOPHE</t>
-  </si>
-  <si>
-    <t>1892</t>
-  </si>
-  <si>
-    <t>"La Comédie humaine (dit aussi Le Masque)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Le_Masque-Ernest_Christophe-IMG_8124-black.jpg/1920px-Le_Masque-Ernest_Christophe-IMG_8124-black.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Camille</t>
-  </si>
-  <si>
-    <t>CLAUDEL</t>
-  </si>
-  <si>
-    <t>1864</t>
-  </si>
-  <si>
-    <t>1943</t>
-  </si>
-  <si>
-    <t>1893</t>
-  </si>
-  <si>
-    <t>Musée Rodin</t>
-  </si>
-  <si>
-    <t>"La Valse"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/62/La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg/960px-La_Valse_de_Camille_Claudel_%28Mus%C3%A9e_Rodin%2C_Paris%29_%2851246445543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>1897</t>
-  </si>
-  <si>
-    <t>"La Vague"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg/960px-Rodin_et_Musee_d%27Orsay_43_%2812176737546%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Bronze, marbre et onyx</t>
-  </si>
-  <si>
-    <t>62 cm environ</t>
-  </si>
-  <si>
-    <t>"L'Âge mûr"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Claudel-2014-05.jpg/1280px-Claudel-2014-05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>CLÉSINGER</t>
-  </si>
-  <si>
-    <t>1814</t>
-  </si>
-  <si>
-    <t>1847</t>
-  </si>
-  <si>
-    <t>"La Femme piquée par un serpent"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Sculpture-7808948_%2852096525415%29.jpg/1280px-Sculpture-7808948_%2852096525415%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>1848</t>
-  </si>
-  <si>
-    <t>"Bacchante couchée"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Paris_8e_-_Petit_Palais_-_Mus%C3%A9e_des_Beaux-Arts_-_Bacchante_%28Auguste_Cl%C3%A9singer%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>Cimetière du Père-Lachaise à Paris</t>
-  </si>
-  <si>
-    <t>"Monument funéraire de Frédéric Chopin"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/64/Chopin_Grave_Grab_Pere_Lachaise.JPG/960px-Chopin_Grave_Grab_Pere_Lachaise.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Charles</t>
-  </si>
-  <si>
-    <t>CORDIER</t>
-  </si>
-  <si>
-    <t>1856-1857</t>
-  </si>
-  <si>
-    <t>"Homme du Soudan"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0b/Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG/960px-Negre_du_Sudan_Charles_Cordier_Mus%C3%A9e_d%27Orsay.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Bronze et onyx polychrome</t>
-  </si>
-  <si>
-    <t>Gustave</t>
-  </si>
-  <si>
-    <t>CRAUK</t>
-  </si>
-  <si>
-    <t>Temple de l’Oratoire du Louvre</t>
-  </si>
-  <si>
-    <t>"Statue de Gaspard de Coligny"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/55/Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg/960px-Statue_of_Gaspard_de_Coligny_%40_Paris_%2832269434936%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Adèle</t>
-  </si>
-  <si>
-    <t>d'AFFRY</t>
-  </si>
-  <si>
-    <t>MARCELLO</t>
-  </si>
-  <si>
-    <t>1836</t>
-  </si>
-  <si>
-    <t>1870</t>
-  </si>
-  <si>
-    <t>Opéra de Paris</t>
-  </si>
-  <si>
-    <t>"Pythie"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/a/a7/Pythia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>suisse</t>
-  </si>
-  <si>
-    <t>Jules</t>
-  </si>
-  <si>
-    <t>DALOU</t>
-  </si>
-  <si>
-    <t>1838</t>
-  </si>
-  <si>
-    <t>1897-1902</t>
-  </si>
-  <si>
-    <t>"Grand paysan"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Dalou_paysan.jpg/960px-Dalou_paysan.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>100 cm environ</t>
-  </si>
-  <si>
-    <t>Place de la Nation</t>
-  </si>
-  <si>
-    <t>"Le Triomphe de la République"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/57/Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg/960px-Paris_11e_-_Place_de_la_Nation_-_Le_Triomphe_de_la_R%C3%A9publique_%28Jules_Dalou%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Pierre-Jean</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>DAVID D'ANGERS</t>
-  </si>
-  <si>
-    <t>1788</t>
-  </si>
-  <si>
-    <t>1856</t>
-  </si>
-  <si>
-    <t>1837</t>
-  </si>
-  <si>
-    <t>Panthéon</t>
-  </si>
-  <si>
-    <t>"Fronton du Panthéon de Paris"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/Fronton_Panth%C3%A9on_Paris_1_reframed.jpg/1280px-Fronton_Panth%C3%A9on_Paris_1_reframed.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>"Philopœmen blessé."</t>
   </si>
   <si>
@@ -970,6 +1063,9 @@
     <t>1844-1951</t>
   </si>
   <si>
+    <t>Florence</t>
+  </si>
+  <si>
     <t>Palazzo Pitti</t>
   </si>
   <si>
@@ -982,9 +1078,6 @@
     <t>170 cm environ</t>
   </si>
   <si>
-    <t>Florence</t>
-  </si>
-  <si>
     <t>Piazzale des Offices</t>
   </si>
   <si>
@@ -1645,9 +1738,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5f/Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg/960px-Pr%C3%A9ault_-_Le_Silence_-_Robl%C3%A8s_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>40 cm environ</t>
-  </si>
-  <si>
     <t>Christian Daniel</t>
   </si>
   <si>
@@ -1786,9 +1876,6 @@
     <t>1855</t>
   </si>
   <si>
-    <t>Metropolitan Museum of Art</t>
-  </si>
-  <si>
     <t>"Nydia, la fleuriste aveugle de Pompéi"</t>
   </si>
   <si>
@@ -1999,27 +2086,6 @@
     <t>210 cm environ</t>
   </si>
   <si>
-    <t>Kōun</t>
-  </si>
-  <si>
-    <t>TAKAMURA</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Parc d'Ueno</t>
-  </si>
-  <si>
-    <t>"Statue de Saigō Takamori"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Statue_SaigoTakamori.JPG/960px-Statue_SaigoTakamori.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>japonaise</t>
-  </si>
-  <si>
     <t>Hamo</t>
   </si>
   <si>
@@ -2174,93 +2240,6 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5a/U.S._Capitol_Samuel_Adams_Statue.jpg/960px-U.S._Capitol_Samuel_Adams_Statue.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>133 cm</t>
-  </si>
-  <si>
-    <t>125 cm</t>
-  </si>
-  <si>
-    <t>95 cm</t>
-  </si>
-  <si>
-    <t>366 cm (statue) 366 cm (piédestal)</t>
-  </si>
-  <si>
-    <t>550 cm</t>
-  </si>
-  <si>
-    <t>1056 cm</t>
-  </si>
-  <si>
-    <t>1906 cm</t>
-  </si>
-  <si>
-    <t>4600 cm (statue) 4700 cm (piédestal)</t>
-  </si>
-  <si>
-    <t>295 cm (statue) 200 cm (piédestal et allégories)</t>
-  </si>
-  <si>
-    <t>1000 cm</t>
-  </si>
-  <si>
-    <t>1800 cm (diamètre)</t>
-  </si>
-  <si>
-    <t>195 cm</t>
-  </si>
-  <si>
-    <t>150 cm</t>
-  </si>
-  <si>
-    <t>110 cm</t>
-  </si>
-  <si>
-    <t>Plâtre patiné</t>
-  </si>
-  <si>
-    <t>194 cm</t>
-  </si>
-  <si>
-    <t>148 cm</t>
-  </si>
-  <si>
-    <t>119 cm</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG/960px-Jean-baptiste_carpeaux%2C_ugolino%2C_1862%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>197,5 cm</t>
-  </si>
-  <si>
-    <t>149,9cm</t>
-  </si>
-  <si>
-    <t>110,5 cm</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Ugolino_and_His_Sons_MET_DP247545.jpg/960px-Ugolino_and_His_Sons_MET_DP247545.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>360 cm environ</t>
-  </si>
-  <si>
-    <t>375 cm</t>
-  </si>
-  <si>
-    <t>141 cm</t>
-  </si>
-  <si>
-    <t>146 cm environ</t>
-  </si>
-  <si>
-    <t>79cm environ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 cm environ </t>
   </si>
 </sst>
 </file>
@@ -2315,7 +2294,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2634,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X123"/>
+  <dimension ref="A1:X122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2810,13 +2789,13 @@
         <v>39</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>718</v>
+        <v>40</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>719</v>
+        <v>41</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>720</v>
+        <v>42</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>35</v>
@@ -2839,7 +2818,7 @@
         <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
@@ -2848,16 +2827,16 @@
         <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W4" t="s">
         <v>35</v>
@@ -2868,40 +2847,40 @@
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>721</v>
+        <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -2909,40 +2888,40 @@
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="S6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>722</v>
+        <v>67</v>
       </c>
       <c r="W6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X6">
         <v>3</v>
@@ -2950,40 +2929,40 @@
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="W7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X7">
         <v>2</v>
@@ -2991,40 +2970,40 @@
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>723</v>
+        <v>83</v>
       </c>
       <c r="U8" t="s">
-        <v>724</v>
+        <v>84</v>
       </c>
       <c r="W8" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X8">
         <v>3</v>
@@ -3032,37 +3011,37 @@
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="M9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>725</v>
+        <v>90</v>
       </c>
       <c r="W9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X9">
         <v>1</v>
@@ -3070,43 +3049,43 @@
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="U10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="W10" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -3114,43 +3093,43 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="U11" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="W11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -3158,13 +3137,13 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -3173,22 +3152,22 @@
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="M12" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="N12" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="W12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X12">
         <v>3</v>
@@ -3196,37 +3175,37 @@
     </row>
     <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J13" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="N13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>726</v>
+        <v>122</v>
       </c>
       <c r="W13" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X13">
         <v>3</v>
@@ -3234,40 +3213,40 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M14" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="N14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>727</v>
+        <v>128</v>
       </c>
       <c r="U14" t="s">
-        <v>728</v>
+        <v>129</v>
       </c>
       <c r="W14" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X14">
         <v>2</v>
@@ -3275,40 +3254,40 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F15" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M15" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="N15" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="W15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X15">
         <v>3</v>
@@ -3316,46 +3295,46 @@
     </row>
     <row r="16" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="S16" s="5" t="s">
         <v>33</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>744</v>
+        <v>146</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>745</v>
+        <v>147</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X16" s="2">
         <v>3</v>
@@ -3363,46 +3342,46 @@
     </row>
     <row r="17" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="S17" s="5" t="s">
         <v>33</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>541</v>
+        <v>153</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>746</v>
+        <v>154</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X17" s="2">
         <v>3</v>
@@ -3410,46 +3389,46 @@
     </row>
     <row r="18" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="S18" s="5" t="s">
         <v>39</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>741</v>
+        <v>164</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>742</v>
+        <v>165</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>743</v>
+        <v>166</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X18" s="2">
         <v>3</v>
@@ -3457,40 +3436,40 @@
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="G19" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="H19" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I19" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J19" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="M19" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="N19" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="W19" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X19">
         <v>3</v>
@@ -3498,46 +3477,46 @@
     </row>
     <row r="20" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>732</v>
+        <v>179</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>729</v>
+        <v>180</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>730</v>
+        <v>181</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>731</v>
+        <v>182</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X20" s="2">
         <v>3</v>
@@ -3545,46 +3524,46 @@
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F21" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M21" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>736</v>
+        <v>183</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>733</v>
+        <v>184</v>
       </c>
       <c r="U21" t="s">
-        <v>734</v>
+        <v>185</v>
       </c>
       <c r="V21" t="s">
-        <v>735</v>
+        <v>186</v>
       </c>
       <c r="W21" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X21">
         <v>3</v>
@@ -3592,46 +3571,46 @@
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F22" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>588</v>
+        <v>187</v>
       </c>
       <c r="M22" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>740</v>
+        <v>188</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>737</v>
+        <v>189</v>
       </c>
       <c r="U22" t="s">
-        <v>738</v>
+        <v>190</v>
       </c>
       <c r="V22" t="s">
-        <v>739</v>
+        <v>191</v>
       </c>
       <c r="W22" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X22">
         <v>3</v>
@@ -3639,46 +3618,46 @@
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F23" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G23" t="s">
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J23" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M23" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="N23" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>733</v>
+        <v>184</v>
       </c>
       <c r="U23" t="s">
-        <v>734</v>
+        <v>185</v>
       </c>
       <c r="V23" t="s">
-        <v>735</v>
+        <v>186</v>
       </c>
       <c r="W23" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -3686,37 +3665,37 @@
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G24" t="s">
         <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J24" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W24" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X24">
         <v>3</v>
@@ -3724,40 +3703,40 @@
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F25" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G25" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="I25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M25" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="N25" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W25" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -3765,40 +3744,40 @@
     </row>
     <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="B26" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F26" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G26" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="H26" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="I26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J26" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M26" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="N26" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W26" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X26">
         <v>3</v>
@@ -3806,37 +3785,37 @@
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F27" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G27" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="H27" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J27" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="M27" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="N27" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="W27" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X27">
         <v>3</v>
@@ -3844,34 +3823,34 @@
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F28" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H28" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="J28" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="M28" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="N28" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W28" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X28">
         <v>3</v>
@@ -3879,40 +3858,40 @@
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="F29" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H29" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="I29" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J29" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M29" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="N29" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W29" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X29">
         <v>3</v>
@@ -3920,40 +3899,40 @@
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="B30" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="F30" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G30" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J30" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="M30" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="N30" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="W30" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X30">
         <v>2</v>
@@ -3961,40 +3940,40 @@
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="F31" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G31" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M31" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="N31" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W31" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X31">
         <v>2</v>
@@ -4002,40 +3981,40 @@
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="F32" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="G32" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="H32" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="I32" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J32" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M32" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="N32" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W32" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -4043,40 +4022,40 @@
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="F33" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="G33" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="H33" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="I33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J33" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M33" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="N33" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="W33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X33">
         <v>3</v>
@@ -4084,37 +4063,37 @@
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="F34" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="G34" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="H34" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I34" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J34" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M34" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="N34" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W34" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X34">
         <v>3</v>
@@ -4122,37 +4101,37 @@
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="F35" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H35" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="I35" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M35" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="N35" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W35" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -4160,37 +4139,37 @@
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B36" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="F36" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H36" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="I36" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J36" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="M36" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="N36" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W36" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X36">
         <v>3</v>
@@ -4198,34 +4177,34 @@
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="F37" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J37" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="N37" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W37" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X37">
         <v>3</v>
@@ -4233,40 +4212,40 @@
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="F38" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H38" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="I38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J38" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M38" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="N38" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W38" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X38">
         <v>2</v>
@@ -4274,37 +4253,37 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H39" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I39" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J39" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="M39" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="N39" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="S39" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W39" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X39">
         <v>2</v>
@@ -4312,34 +4291,34 @@
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="E40" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="J40" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="S40" s="3" t="s">
         <v>39</v>
@@ -4348,7 +4327,7 @@
         <v>34</v>
       </c>
       <c r="W40" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="X40">
         <v>2</v>
@@ -4356,40 +4335,40 @@
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="F41" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="G41" t="s">
         <v>27</v>
       </c>
       <c r="H41" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="I41" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J41" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M41" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="N41" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="W41" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X41">
         <v>3</v>
@@ -4397,37 +4376,37 @@
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="F42" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="G42" t="s">
         <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J42" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W42" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X42">
         <v>1</v>
@@ -4435,43 +4414,43 @@
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D43" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="E43" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="F43" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G43" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="H43" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="I43" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J43" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="M43" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="N43" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="W43" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -4479,46 +4458,46 @@
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D44" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="E44" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="F44" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G44" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="H44" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="I44" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J44" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M44" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="N44" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="W44" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X44">
         <v>3</v>
@@ -4526,46 +4505,46 @@
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D45" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="E45" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="F45" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="G45" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="H45" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="I45" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="J45" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="M45" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="N45" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W45" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X45">
         <v>3</v>
@@ -4573,40 +4552,40 @@
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="F46" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H46" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="I46" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J46" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="M46" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="N46" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="W46" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -4614,37 +4593,37 @@
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="B47" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H47" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J47" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="M47" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="N47" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="W47" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X47">
         <v>3</v>
@@ -4652,37 +4631,37 @@
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H48" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="I48" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J48" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="M48" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="N48" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="W48" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X48">
         <v>3</v>
@@ -4690,40 +4669,40 @@
     </row>
     <row r="49" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="F49" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="G49" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H49" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="I49" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J49" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M49" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="N49" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W49" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X49">
         <v>2</v>
@@ -4731,40 +4710,40 @@
     </row>
     <row r="50" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="F50" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="G50" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H50" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I50" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J50" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="M50" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="N50" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="W50" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X50">
         <v>3</v>
@@ -4772,37 +4751,37 @@
     </row>
     <row r="51" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="F51" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="G51" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H51" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I51" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="J51" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="M51" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="N51" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="S51" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W51" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X51">
         <v>3</v>
@@ -4810,40 +4789,40 @@
     </row>
     <row r="52" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="S52" s="5" t="s">
         <v>33</v>
       </c>
       <c r="T52" s="5" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X52" s="2">
         <v>2</v>
@@ -4851,37 +4830,37 @@
     </row>
     <row r="53" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="F53" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G53" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="H53" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I53" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="J53" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="M53" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="N53" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="S53" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W53" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X53">
         <v>3</v>
@@ -4889,37 +4868,37 @@
     </row>
     <row r="54" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="F54" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="G54" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="H54" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="I54" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J54" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="M54" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="N54" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="W54" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X54">
         <v>3</v>
@@ -4927,40 +4906,40 @@
     </row>
     <row r="55" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B55" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="F55" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G55" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="H55" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="I55" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J55" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M55" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="N55" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="S55" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W55" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X55">
         <v>2</v>
@@ -4968,40 +4947,40 @@
     </row>
     <row r="56" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="F56" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G56" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="H56" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="I56" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J56" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M56" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="N56" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="S56" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W56" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X56">
         <v>3</v>
@@ -5009,37 +4988,37 @@
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="F57" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G57" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="H57" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="I57" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J57" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M57" t="s">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="N57" t="s">
-        <v>341</v>
+        <v>372</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W57" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X57">
         <v>3</v>
@@ -5047,40 +5026,40 @@
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="F58" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="G58" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H58" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="I58" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="J58" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="N58" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="W58" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X58">
         <v>2</v>
@@ -5088,37 +5067,37 @@
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>342</v>
+        <v>373</v>
       </c>
       <c r="B59" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="F59" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="G59" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I59" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="J59" t="s">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s">
-        <v>349</v>
+        <v>380</v>
       </c>
       <c r="N59" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W59" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X59">
         <v>3</v>
@@ -5126,37 +5105,37 @@
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G60" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H60" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I60" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J60" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="M60" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="N60" t="s">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W60" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X60">
         <v>3</v>
@@ -5164,40 +5143,40 @@
     </row>
     <row r="61" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F61" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G61" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H61" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="I61" t="s">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="J61" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="M61" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="N61" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W61" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -5205,34 +5184,34 @@
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F62" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G62" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H62" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="J62" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="M62" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="N62" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="W62" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X62">
         <v>3</v>
@@ -5240,37 +5219,37 @@
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>351</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G63" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="H63" t="s">
-        <v>364</v>
+        <v>395</v>
       </c>
       <c r="I63" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J63" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="W63" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X63">
         <v>3</v>
@@ -5278,37 +5257,37 @@
     </row>
     <row r="64" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="B64" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="F64" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H64" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="J64" t="s">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="M64" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="N64" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="S64" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="W64" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="X64">
         <v>3</v>
@@ -5316,40 +5295,40 @@
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="B65" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="F65" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="G65" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="H65" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="I65" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="J65" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="M65" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="N65" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="S65" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W65" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X65">
         <v>2</v>
@@ -5357,40 +5336,40 @@
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>375</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="F66" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="G66" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="H66" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="I66" t="s">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="J66" t="s">
-        <v>383</v>
+        <v>414</v>
       </c>
       <c r="M66" t="s">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="N66" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W66" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="X66">
         <v>3</v>
@@ -5398,40 +5377,40 @@
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="B67" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="F67" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="G67" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I67" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J67" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M67" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="N67" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>390</v>
+        <v>421</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W67" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X67">
         <v>1</v>
@@ -5439,40 +5418,40 @@
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="B68" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="F68" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="G68" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="H68" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="I68" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="J68" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="M68" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="N68" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="W68" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X68">
         <v>1</v>
@@ -5480,37 +5459,37 @@
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B69" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="F69" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="G69" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H69" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="I69" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="J69" t="s">
-        <v>403</v>
+        <v>434</v>
       </c>
       <c r="M69" t="s">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="N69" t="s">
-        <v>405</v>
+        <v>436</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="W69" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X69">
         <v>3</v>
@@ -5518,37 +5497,37 @@
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="F70" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="G70" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="H70" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="I70" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
       <c r="J70" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="M70" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="N70" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="W70" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="X70">
         <v>2</v>
@@ -5556,40 +5535,40 @@
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="F71" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="G71" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="H71" t="s">
-        <v>421</v>
+        <v>452</v>
       </c>
       <c r="I71" t="s">
-        <v>422</v>
+        <v>453</v>
       </c>
       <c r="J71" t="s">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="M71" t="s">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="N71" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="S71" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="W71" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X71">
         <v>2</v>
@@ -5597,31 +5576,31 @@
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="B72" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="F72" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G72" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="H72" t="s">
-        <v>430</v>
+        <v>461</v>
       </c>
       <c r="I72" t="s">
         <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>431</v>
+        <v>462</v>
       </c>
       <c r="M72" t="s">
-        <v>432</v>
+        <v>463</v>
       </c>
       <c r="N72" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>33</v>
@@ -5635,28 +5614,28 @@
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="F73" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G73" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="H73" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="J73" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="N73" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="S73" s="3" t="s">
         <v>33</v>
@@ -5670,37 +5649,37 @@
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>438</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s">
-        <v>439</v>
+        <v>470</v>
       </c>
       <c r="F74" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="G74" t="s">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="H74" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="I74" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="J74" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="M74" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="N74" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="S74" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W74" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -5708,40 +5687,40 @@
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="F75" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="G75" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="H75" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="I75" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="J75" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="M75" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="N75" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="S75" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T75" s="3" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="W75" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X75">
         <v>2</v>
@@ -5749,40 +5728,40 @@
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B76" t="s">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="F76" t="s">
-        <v>419</v>
+        <v>450</v>
       </c>
       <c r="G76" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="H76" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="I76" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="J76" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="M76" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="N76" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="W76" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X76">
         <v>3</v>
@@ -5790,40 +5769,40 @@
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="F77" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="G77" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="H77" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I77" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J77" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="M77" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
       <c r="N77" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="W77" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X77">
         <v>1</v>
@@ -5831,40 +5810,40 @@
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="B78" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="F78" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G78" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="H78" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I78" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J78" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M78" t="s">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="N78" t="s">
-        <v>469</v>
+        <v>500</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="W78" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X78">
         <v>3</v>
@@ -5872,40 +5851,40 @@
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="B79" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="F79" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G79" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="H79" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="I79" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J79" t="s">
-        <v>470</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="S79" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T79" s="3" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="W79" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X79">
         <v>1</v>
@@ -5913,40 +5892,40 @@
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="F80" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G80" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H80" t="s">
-        <v>476</v>
+        <v>507</v>
       </c>
       <c r="I80" t="s">
-        <v>441</v>
+        <v>472</v>
       </c>
       <c r="J80" t="s">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="N80" t="s">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="S80" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T80" s="3" t="s">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="W80" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="X80">
         <v>2</v>
@@ -5954,37 +5933,37 @@
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="B81" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="F81" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G81" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H81" t="s">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="I81" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J81" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="M81" t="s">
-        <v>483</v>
+        <v>514</v>
       </c>
       <c r="N81" t="s">
-        <v>484</v>
+        <v>515</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="W81" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X81">
         <v>3</v>
@@ -5992,37 +5971,37 @@
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>480</v>
+        <v>511</v>
       </c>
       <c r="B82" t="s">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="F82" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G82" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H82" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="I82" t="s">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="J82" t="s">
-        <v>487</v>
+        <v>518</v>
       </c>
       <c r="M82" t="s">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="N82" t="s">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="W82" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X82">
         <v>2</v>
@@ -6030,37 +6009,37 @@
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B83" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="F83" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G83" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="H83" t="s">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="I83" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="J83" t="s">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="M83" t="s">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="N83" t="s">
-        <v>497</v>
+        <v>528</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="W83" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X83">
         <v>3</v>
@@ -6068,37 +6047,37 @@
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B84" t="s">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="F84" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G84" t="s">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="H84" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="I84" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J84" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M84" t="s">
-        <v>499</v>
+        <v>530</v>
       </c>
       <c r="N84" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="S84" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W84" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X84">
         <v>3</v>
@@ -6106,37 +6085,37 @@
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="B85" t="s">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="F85" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="G85" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="H85" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="I85" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="J85" t="s">
-        <v>506</v>
+        <v>537</v>
       </c>
       <c r="M85" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
       <c r="N85" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="S85" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W85" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="X85">
         <v>1</v>
@@ -6144,40 +6123,40 @@
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="B86" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="F86" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G86" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H86" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I86" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J86" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M86" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="N86" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="S86" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T86" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="W86" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X86">
         <v>3</v>
@@ -6185,37 +6164,37 @@
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="B87" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="F87" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="G87" t="s">
         <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="I87" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="J87" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="M87" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="N87" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="S87" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W87" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="X87">
         <v>2</v>
@@ -6223,40 +6202,40 @@
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="B88" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="F88" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G88" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="H88" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="I88" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J88" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="M88" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="N88" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="S88" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T88" s="3" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="W88" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -6264,40 +6243,40 @@
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B89" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="F89" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="G89" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="H89" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I89" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J89" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M89" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="N89" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T89" s="3" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="W89" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="X89">
         <v>3</v>
@@ -6305,40 +6284,40 @@
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B90" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="F90" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="G90" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="H90" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J90" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M90" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="N90" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="S90" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T90" s="3" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="W90" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="X90">
         <v>1</v>
@@ -6346,40 +6325,40 @@
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B91" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="F91" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="G91" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="I91" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J91" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="M91" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="N91" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T91" s="3" t="s">
-        <v>541</v>
+        <v>153</v>
       </c>
       <c r="W91" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X91">
         <v>2</v>
@@ -6387,37 +6366,37 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="F92" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G92" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="H92" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="I92" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J92" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="M92" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="N92" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="S92" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W92" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X92">
         <v>2</v>
@@ -6425,40 +6404,40 @@
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="B93" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="F93" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="G93" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="H93" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="I93" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="J93" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="M93" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="N93" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="S93" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T93" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W93" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -6466,37 +6445,37 @@
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="B94" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="F94" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="G94" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="H94" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="I94" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="J94" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="M94" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="N94" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W94" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X94">
         <v>2</v>
@@ -6504,40 +6483,40 @@
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B95" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="F95" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="G95" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H95" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="I95" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J95" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="M95" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="N95" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="S95" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T95" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="W95" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X95">
         <v>3</v>
@@ -6545,40 +6524,40 @@
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B96" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="F96" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="G96" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H96" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="I96" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J96" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M96" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="N96" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="S96" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T96" s="3" t="s">
-        <v>570</v>
+        <v>600</v>
       </c>
       <c r="W96" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -6586,37 +6565,37 @@
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="F97" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="G97" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H97" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
       <c r="I97" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J97" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M97" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="N97" t="s">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="S97" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W97" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X97">
         <v>3</v>
@@ -6624,40 +6603,40 @@
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B98" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="F98" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="G98" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H98" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="I98" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="J98" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="M98" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="N98" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="S98" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T98" s="3" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="W98" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X98">
         <v>3</v>
@@ -6665,40 +6644,40 @@
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B99" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="F99" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="G99" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="H99" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="I99" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J99" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="M99" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="N99" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="S99" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T99" s="3" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="W99" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X99">
         <v>3</v>
@@ -6706,40 +6685,40 @@
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="B100" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="F100" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="G100" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H100" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="I100" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J100" t="s">
-        <v>588</v>
+        <v>187</v>
       </c>
       <c r="M100" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="N100" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T100" s="3" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="W100" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X100">
         <v>1</v>
@@ -6747,37 +6726,37 @@
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="F101" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
       <c r="G101" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H101" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="I101" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="J101" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="M101" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="N101" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>39</v>
       </c>
       <c r="W101" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X101">
         <v>3</v>
@@ -6785,40 +6764,40 @@
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B102" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F102" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G102" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H102" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I102" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J102" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M102" t="s">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="N102" t="s">
-        <v>600</v>
+        <v>629</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W102" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X102">
         <v>3</v>
@@ -6826,40 +6805,40 @@
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B103" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F103" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G103" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H103" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I103" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="J103" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="M103" t="s">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="N103" t="s">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="S103" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T103" s="3" t="s">
-        <v>605</v>
+        <v>634</v>
       </c>
       <c r="W103" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X103">
         <v>3</v>
@@ -6867,40 +6846,40 @@
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F104" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G104" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H104" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="I104" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J104" t="s">
-        <v>588</v>
+        <v>187</v>
       </c>
       <c r="M104" t="s">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="N104" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="S104" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T104" s="3" t="s">
-        <v>541</v>
+        <v>153</v>
       </c>
       <c r="W104" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X104">
         <v>3</v>
@@ -6908,37 +6887,37 @@
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B105" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F105" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G105" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H105" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I105" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J105" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="M105" t="s">
-        <v>608</v>
+        <v>637</v>
       </c>
       <c r="N105" t="s">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="S105" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="W105" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X105">
         <v>1</v>
@@ -6946,37 +6925,37 @@
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B106" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F106" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G106" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H106" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="I106" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J106" t="s">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="M106" t="s">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="N106" t="s">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="S106" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="W106" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X106">
         <v>3</v>
@@ -6984,40 +6963,40 @@
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B107" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="F107" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G107" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
       <c r="H107" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="I107" t="s">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="J107" t="s">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="M107" t="s">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="N107" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="S107" s="3" t="s">
         <v>33</v>
       </c>
       <c r="T107" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="W107" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X107">
         <v>3</v>
@@ -7025,37 +7004,37 @@
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="B108" t="s">
-        <v>618</v>
+        <v>647</v>
       </c>
       <c r="F108" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="G108" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="H108" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="I108" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="J108" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="M108" t="s">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="N108" t="s">
-        <v>622</v>
+        <v>651</v>
       </c>
       <c r="S108" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W108" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X108">
         <v>1</v>
@@ -7063,37 +7042,37 @@
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="B109" t="s">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="F109" t="s">
-        <v>625</v>
+        <v>654</v>
       </c>
       <c r="G109" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H109" t="s">
-        <v>626</v>
+        <v>655</v>
       </c>
       <c r="I109" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J109" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="M109" t="s">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="N109" t="s">
-        <v>629</v>
+        <v>658</v>
       </c>
       <c r="S109" s="3" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="W109" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X109">
         <v>2</v>
@@ -7101,37 +7080,37 @@
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="B110" t="s">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="F110" t="s">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="G110" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H110" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="I110" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="J110" t="s">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="M110" t="s">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="N110" t="s">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="S110" s="3" t="s">
         <v>33</v>
       </c>
       <c r="W110" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X110">
         <v>2</v>
@@ -7139,40 +7118,40 @@
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>635</v>
+        <v>664</v>
       </c>
       <c r="B111" t="s">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="F111" t="s">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="G111" t="s">
-        <v>503</v>
+        <v>534</v>
       </c>
       <c r="H111" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="I111" t="s">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="J111" t="s">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="M111" t="s">
-        <v>640</v>
+        <v>669</v>
       </c>
       <c r="N111" t="s">
-        <v>641</v>
+        <v>670</v>
       </c>
       <c r="S111" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T111" s="3" t="s">
-        <v>642</v>
+        <v>671</v>
       </c>
       <c r="W111" t="s">
-        <v>643</v>
+        <v>672</v>
       </c>
       <c r="X111">
         <v>2</v>
@@ -7180,37 +7159,37 @@
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B112" t="s">
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="F112" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G112" t="s">
         <v>36</v>
       </c>
       <c r="H112" t="s">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="I112" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="J112" t="s">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="M112" t="s">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="N112" t="s">
-        <v>647</v>
+        <v>676</v>
       </c>
       <c r="S112" s="3" t="s">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="W112" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="X112">
         <v>3</v>
@@ -7218,40 +7197,40 @@
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="B113" t="s">
-        <v>650</v>
+        <v>679</v>
       </c>
       <c r="F113" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G113" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="H113" t="s">
-        <v>651</v>
+        <v>680</v>
       </c>
       <c r="I113" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J113" t="s">
-        <v>588</v>
+        <v>187</v>
       </c>
       <c r="M113" t="s">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="N113" t="s">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="S113" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T113" s="3" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="W113" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X113">
         <v>2</v>
@@ -7259,37 +7238,37 @@
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>649</v>
+        <v>678</v>
       </c>
       <c r="B114" t="s">
-        <v>650</v>
+        <v>679</v>
       </c>
       <c r="F114" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G114" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="H114" t="s">
-        <v>654</v>
+        <v>683</v>
       </c>
       <c r="J114" t="s">
-        <v>655</v>
+        <v>684</v>
       </c>
       <c r="M114" t="s">
-        <v>656</v>
+        <v>685</v>
       </c>
       <c r="N114" t="s">
-        <v>657</v>
+        <v>686</v>
       </c>
       <c r="S114" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T114" s="3" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="W114" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X114">
         <v>3</v>
@@ -7297,37 +7276,40 @@
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>659</v>
+        <v>688</v>
       </c>
       <c r="B115" t="s">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="F115" t="s">
-        <v>377</v>
+        <v>94</v>
       </c>
       <c r="G115" t="s">
-        <v>129</v>
+        <v>690</v>
       </c>
       <c r="H115" t="s">
-        <v>580</v>
+        <v>691</v>
       </c>
       <c r="I115" t="s">
-        <v>661</v>
+        <v>433</v>
       </c>
       <c r="J115" t="s">
-        <v>662</v>
+        <v>480</v>
       </c>
       <c r="M115" t="s">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="N115" t="s">
-        <v>664</v>
+        <v>693</v>
       </c>
       <c r="S115" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="T115" s="3" t="s">
+        <v>404</v>
+      </c>
       <c r="W115" t="s">
-        <v>665</v>
+        <v>222</v>
       </c>
       <c r="X115">
         <v>2</v>
@@ -7335,321 +7317,280 @@
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="B116" t="s">
+        <v>695</v>
+      </c>
+      <c r="F116" t="s">
+        <v>696</v>
+      </c>
+      <c r="G116" t="s">
+        <v>490</v>
+      </c>
+      <c r="H116" t="s">
+        <v>697</v>
+      </c>
+      <c r="I116" t="s">
         <v>667</v>
       </c>
-      <c r="F116" t="s">
-        <v>86</v>
-      </c>
-      <c r="G116" t="s">
-        <v>668</v>
-      </c>
-      <c r="H116" t="s">
-        <v>669</v>
-      </c>
-      <c r="I116" t="s">
-        <v>402</v>
-      </c>
       <c r="J116" t="s">
-        <v>449</v>
+        <v>698</v>
       </c>
       <c r="M116" t="s">
-        <v>670</v>
+        <v>699</v>
       </c>
       <c r="N116" t="s">
-        <v>671</v>
+        <v>700</v>
       </c>
       <c r="S116" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="T116" s="3" t="s">
-        <v>373</v>
+        <v>701</v>
       </c>
       <c r="W116" t="s">
-        <v>192</v>
+        <v>702</v>
       </c>
       <c r="X116">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>672</v>
+        <v>694</v>
       </c>
       <c r="B117" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
       <c r="F117" t="s">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="G117" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="H117" t="s">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="I117" t="s">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="J117" t="s">
-        <v>676</v>
+        <v>704</v>
       </c>
       <c r="M117" t="s">
-        <v>677</v>
+        <v>705</v>
       </c>
       <c r="N117" t="s">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="S117" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T117" s="3" t="s">
-        <v>679</v>
+        <v>707</v>
       </c>
       <c r="W117" t="s">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="X117">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>672</v>
+        <v>406</v>
       </c>
       <c r="B118" t="s">
-        <v>673</v>
+        <v>708</v>
       </c>
       <c r="F118" t="s">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="G118" t="s">
-        <v>459</v>
+        <v>124</v>
       </c>
       <c r="H118" t="s">
-        <v>681</v>
-      </c>
-      <c r="I118" t="s">
-        <v>638</v>
+        <v>207</v>
       </c>
       <c r="J118" t="s">
-        <v>682</v>
+        <v>710</v>
       </c>
       <c r="M118" t="s">
-        <v>683</v>
+        <v>711</v>
       </c>
       <c r="N118" t="s">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="S118" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T118" s="3" t="s">
-        <v>685</v>
-      </c>
       <c r="W118" t="s">
-        <v>680</v>
+        <v>283</v>
       </c>
       <c r="X118">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>375</v>
+        <v>713</v>
       </c>
       <c r="B119" t="s">
-        <v>686</v>
+        <v>714</v>
       </c>
       <c r="F119" t="s">
-        <v>687</v>
+        <v>715</v>
       </c>
       <c r="G119" t="s">
-        <v>115</v>
+        <v>716</v>
       </c>
       <c r="H119" t="s">
-        <v>177</v>
+        <v>717</v>
+      </c>
+      <c r="I119" t="s">
+        <v>718</v>
       </c>
       <c r="J119" t="s">
-        <v>688</v>
+        <v>719</v>
       </c>
       <c r="M119" t="s">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="N119" t="s">
-        <v>690</v>
+        <v>721</v>
       </c>
       <c r="S119" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="W119" t="s">
-        <v>252</v>
+        <v>552</v>
       </c>
       <c r="X119">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>691</v>
+        <v>722</v>
       </c>
       <c r="B120" t="s">
-        <v>692</v>
+        <v>723</v>
       </c>
       <c r="F120" t="s">
-        <v>693</v>
+        <v>255</v>
       </c>
       <c r="G120" t="s">
-        <v>694</v>
+        <v>724</v>
       </c>
       <c r="H120" t="s">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="I120" t="s">
-        <v>696</v>
+        <v>125</v>
       </c>
       <c r="J120" t="s">
-        <v>697</v>
+        <v>594</v>
       </c>
       <c r="M120" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="N120" t="s">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="S120" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="T120" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="W120" t="s">
-        <v>521</v>
+        <v>123</v>
       </c>
       <c r="X120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="B121" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="F121" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="G121" t="s">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="H121" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="I121" t="s">
-        <v>116</v>
+        <v>729</v>
       </c>
       <c r="J121" t="s">
-        <v>564</v>
+        <v>730</v>
       </c>
       <c r="M121" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="N121" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="S121" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T121" s="3" t="s">
-        <v>176</v>
+        <v>733</v>
       </c>
       <c r="W121" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="X121">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>700</v>
+        <v>734</v>
       </c>
       <c r="B122" t="s">
-        <v>701</v>
+        <v>735</v>
       </c>
       <c r="F122" t="s">
-        <v>224</v>
+        <v>703</v>
       </c>
       <c r="G122" t="s">
-        <v>702</v>
+        <v>736</v>
       </c>
       <c r="H122" t="s">
-        <v>706</v>
+        <v>51</v>
       </c>
       <c r="I122" t="s">
-        <v>707</v>
+        <v>52</v>
       </c>
       <c r="J122" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="M122" t="s">
-        <v>709</v>
+        <v>738</v>
       </c>
       <c r="N122" t="s">
-        <v>710</v>
+        <v>739</v>
       </c>
       <c r="S122" s="3" t="s">
-        <v>711</v>
+        <v>39</v>
       </c>
       <c r="W122" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="X122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>712</v>
-      </c>
-      <c r="B123" t="s">
-        <v>713</v>
-      </c>
-      <c r="F123" t="s">
-        <v>681</v>
-      </c>
-      <c r="G123" t="s">
-        <v>714</v>
-      </c>
-      <c r="H123" t="s">
-        <v>48</v>
-      </c>
-      <c r="I123" t="s">
-        <v>49</v>
-      </c>
-      <c r="J123" t="s">
-        <v>715</v>
-      </c>
-      <c r="M123" t="s">
-        <v>716</v>
-      </c>
-      <c r="N123" t="s">
-        <v>717</v>
-      </c>
-      <c r="S123" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="W123" t="s">
-        <v>53</v>
-      </c>
-      <c r="X123">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N21" r:id="rId1" xr:uid="{347500AD-78A8-4CDD-952C-E47BD4F93F86}"/>
-    <hyperlink ref="N22" r:id="rId2" xr:uid="{7157D416-FEAD-4926-9F17-F376F79B410A}"/>
+    <hyperlink ref="N21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16ADF6D-CB89-44D4-875E-6E429B9B6D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="687">
   <si>
     <t>Prénom</t>
   </si>
@@ -835,9 +841,6 @@
     <t>Munich</t>
   </si>
   <si>
-    <t>Musée russe</t>
-  </si>
-  <si>
     <t>Lincoln Park</t>
   </si>
   <si>
@@ -877,9 +880,6 @@
     <t>Metropolitan Museum of Art</t>
   </si>
   <si>
-    <t>Jardin des Grands Explorateurs (de l'Observatoire)</t>
-  </si>
-  <si>
     <t>Palais Garnier</t>
   </si>
   <si>
@@ -973,9 +973,6 @@
     <t>Place Saint-Isaac à Saint-Pétersbourg</t>
   </si>
   <si>
-    <t>Pavillon des Passions humaines, Parc du Cinquantenaire</t>
-  </si>
-  <si>
     <t>Tate Britain</t>
   </si>
   <si>
@@ -1039,9 +1036,6 @@
     <t>Porte de Brandebourg</t>
   </si>
   <si>
-    <t>Eakins Oval (autrefois Fairmount Park)</t>
-  </si>
-  <si>
     <t>Ny Carlsberg Glyptotek</t>
   </si>
   <si>
@@ -1105,9 +1099,6 @@
     <t>"Mémorial Schiller"</t>
   </si>
   <si>
-    <t>"Neptunbrunnen (Fontaine de Neptune)"</t>
-  </si>
-  <si>
     <t>"La Nymphe Salmacis"</t>
   </si>
   <si>
@@ -1150,9 +1141,6 @@
     <t>"La Jeunesse"</t>
   </si>
   <si>
-    <t>"La Comédie humaine (dit aussi Le Masque)"</t>
-  </si>
-  <si>
     <t>"La Valse"</t>
   </si>
   <si>
@@ -1195,18 +1183,12 @@
     <t>"Le jeune Barra"</t>
   </si>
   <si>
-    <t>"La Petite Danseuse de quatorze ans (1er modèle en cire)"</t>
-  </si>
-  <si>
     <t>"LeTemps fauchant les amours"</t>
   </si>
   <si>
     <t>"Monument à Alexandre Dumas"</t>
   </si>
   <si>
-    <t>"Le Chanteur florentin (Le Condottiere)"</t>
-  </si>
-  <si>
     <t>"Ève naissante"</t>
   </si>
   <si>
@@ -1261,9 +1243,6 @@
     <t>"Tanagra"</t>
   </si>
   <si>
-    <t>"La Vénus teintée (Tinted Venus)"</t>
-  </si>
-  <si>
     <t>"La Fontaine d'Éros"</t>
   </si>
   <si>
@@ -1273,9 +1252,6 @@
     <t>"Zenobia enchaînée"</t>
   </si>
   <si>
-    <t>"Les Chevaux dressés (groupe du pont Anitchkov)"</t>
-  </si>
-  <si>
     <t>"Statue de l'empereur Nicolas Ier"</t>
   </si>
   <si>
@@ -1297,12 +1273,6 @@
     <t>"Gloria Victis"</t>
   </si>
   <si>
-    <t>"Le Semeur (L'Automne)"</t>
-  </si>
-  <si>
-    <t>"Apollon, la Poésie et la Musique. Toit du Palais Garnier"</t>
-  </si>
-  <si>
     <t>"Statue de Vercingétorix"</t>
   </si>
   <si>
@@ -1318,9 +1288,6 @@
     <t>"Le Désespoir"</t>
   </si>
   <si>
-    <t>"Reliefs en bronze du monument à Cervantès (Don Quichotte et Sancho Pança)"</t>
-  </si>
-  <si>
     <t>"L'Esclave grecque"</t>
   </si>
   <si>
@@ -1372,9 +1339,6 @@
     <t>"Tête du Guerrier"</t>
   </si>
   <si>
-    <t>"Le Départ des volontaires de 1792 (La Marseillaise)"</t>
-  </si>
-  <si>
     <t>"Le Baptême du Christ"</t>
   </si>
   <si>
@@ -1390,9 +1354,6 @@
     <t>"Monument national à Washington"</t>
   </si>
   <si>
-    <t>"Mère captive (Den fangne mor)"</t>
-  </si>
-  <si>
     <t>"Monument au duc de Wellington"</t>
   </si>
   <si>
@@ -1420,9 +1381,6 @@
     <t>"Jeune pâtre endormi"</t>
   </si>
   <si>
-    <t>"Fontaine Wittelsbach (Wittelsbacherbrunnen)"</t>
-  </si>
-  <si>
     <t>"Samuel Adams"</t>
   </si>
   <si>
@@ -2072,13 +2030,64 @@
   </si>
   <si>
     <t>danoise</t>
+  </si>
+  <si>
+    <t>Musée Russe</t>
+  </si>
+  <si>
+    <t>Fontaine de Neptune</t>
+  </si>
+  <si>
+    <t>"La Comédie humaine"</t>
+  </si>
+  <si>
+    <t>"La Petite Danseuse de quatorze ans"</t>
+  </si>
+  <si>
+    <t>"Le Chanteur florentin"</t>
+  </si>
+  <si>
+    <t>"La Vénus teintée"</t>
+  </si>
+  <si>
+    <t>"Les Chevaux dressés"</t>
+  </si>
+  <si>
+    <t>"Le Semeur"</t>
+  </si>
+  <si>
+    <t>"Apollon, la Poésie et la Musique."</t>
+  </si>
+  <si>
+    <t>"Reliefs en bronze du monument à Cervantès"</t>
+  </si>
+  <si>
+    <t>"Le Départ des volontaires de 1792"</t>
+  </si>
+  <si>
+    <t>"Mère captive"</t>
+  </si>
+  <si>
+    <t>"Fontaine Wittelsbach"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eakins Oval </t>
+  </si>
+  <si>
+    <t>Parc du Cinquantenaire</t>
+  </si>
+  <si>
+    <t>Jardin des Grands Explorateurs</t>
+  </si>
+  <si>
+    <t>Bronze et graniyte rose</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2123,18 +2132,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2172,7 +2189,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2206,6 +2223,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2240,9 +2258,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2415,11 +2434,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X122"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="30.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
+    <col min="13" max="13" width="72.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2493,7 +2517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -2513,28 +2537,28 @@
         <v>239</v>
       </c>
       <c r="J2" t="s">
-        <v>273</v>
+        <v>670</v>
       </c>
       <c r="M2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="S2" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T2" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="W2" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="X2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2554,34 +2578,34 @@
         <v>239</v>
       </c>
       <c r="J3" t="s">
-        <v>273</v>
+        <v>670</v>
       </c>
       <c r="M3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="S3" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T3" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="U3" t="s">
+        <v>641</v>
+      </c>
+      <c r="V3" t="s">
+        <v>650</v>
+      </c>
+      <c r="W3" t="s">
         <v>657</v>
-      </c>
-      <c r="V3" t="s">
-        <v>666</v>
-      </c>
-      <c r="W3" t="s">
-        <v>673</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2601,28 +2625,28 @@
         <v>239</v>
       </c>
       <c r="J4" t="s">
-        <v>273</v>
+        <v>670</v>
       </c>
       <c r="M4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="S4" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T4" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W4" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="X4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2642,28 +2666,28 @@
         <v>240</v>
       </c>
       <c r="J5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="S5" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T5" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="W5" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -2683,28 +2707,28 @@
         <v>241</v>
       </c>
       <c r="J6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="S6" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T6" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="W6" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2724,28 +2748,28 @@
         <v>241</v>
       </c>
       <c r="J7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="S7" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="T7" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="W7" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2762,31 +2786,31 @@
         <v>162</v>
       </c>
       <c r="J8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M8" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="S8" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="T8" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="U8" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="W8" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -2806,25 +2830,25 @@
         <v>246</v>
       </c>
       <c r="M9" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="S9" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="T9" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="W9" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2844,31 +2868,31 @@
         <v>241</v>
       </c>
       <c r="J10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="S10" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T10" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="U10" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="W10" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -2888,31 +2912,31 @@
         <v>241</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M11" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="S11" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T11" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="U11" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="W11" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2929,28 +2953,28 @@
         <v>166</v>
       </c>
       <c r="J12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M12" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="S12" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T12" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="W12" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2966,29 +2990,32 @@
       <c r="H13" t="s">
         <v>167</v>
       </c>
+      <c r="I13" t="s">
+        <v>262</v>
+      </c>
       <c r="J13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M13" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="S13" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="T13" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="W13" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3004,32 +3031,32 @@
       <c r="H14" t="s">
         <v>168</v>
       </c>
-      <c r="J14" t="s">
+      <c r="I14" t="s">
         <v>262</v>
       </c>
       <c r="M14" t="s">
-        <v>363</v>
+        <v>671</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="S14" t="s">
-        <v>596</v>
+        <v>686</v>
       </c>
       <c r="T14" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="U14" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="W14" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -3049,28 +3076,28 @@
         <v>241</v>
       </c>
       <c r="J15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M15" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="S15" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T15" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="W15" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3090,34 +3117,34 @@
         <v>242</v>
       </c>
       <c r="J16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M16" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="S16" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T16" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="U16" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="V16" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="W16" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X16">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3137,34 +3164,34 @@
         <v>243</v>
       </c>
       <c r="J17" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M17" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="S17" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T17" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="U17" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="V17" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="W17" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -3184,34 +3211,34 @@
         <v>244</v>
       </c>
       <c r="J18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M18" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="S18" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T18" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="U18" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="V18" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="W18" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -3231,28 +3258,28 @@
         <v>245</v>
       </c>
       <c r="J19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M19" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="S19" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T19" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="W19" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X19">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -3272,34 +3299,34 @@
         <v>241</v>
       </c>
       <c r="J20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M20" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="S20" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="T20" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="U20" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="V20" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="W20" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -3319,34 +3346,34 @@
         <v>241</v>
       </c>
       <c r="J21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M21" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="S21" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T21" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="U21" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="V21" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="W21" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X21">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -3366,34 +3393,34 @@
         <v>246</v>
       </c>
       <c r="J22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M22" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="S22" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T22" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="U22" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="V22" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="W22" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -3413,34 +3440,34 @@
         <v>241</v>
       </c>
       <c r="J23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="S23" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T23" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="U23" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="V23" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="W23" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3460,25 +3487,25 @@
         <v>241</v>
       </c>
       <c r="J24" t="s">
-        <v>287</v>
+        <v>685</v>
       </c>
       <c r="M24" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="S24" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W24" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -3498,28 +3525,28 @@
         <v>241</v>
       </c>
       <c r="J25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="S25" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T25" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W25" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -3539,28 +3566,28 @@
         <v>241</v>
       </c>
       <c r="J26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="S26" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T26" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W26" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -3580,25 +3607,25 @@
         <v>241</v>
       </c>
       <c r="J27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M27" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="S27" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="W27" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3615,25 +3642,25 @@
         <v>179</v>
       </c>
       <c r="J28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="S28" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W28" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X28">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3653,28 +3680,28 @@
         <v>241</v>
       </c>
       <c r="J29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="S29" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T29" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W29" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X29">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -3694,28 +3721,28 @@
         <v>241</v>
       </c>
       <c r="J30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="S30" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T30" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="W30" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -3735,28 +3762,28 @@
         <v>241</v>
       </c>
       <c r="J31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s">
-        <v>378</v>
+        <v>672</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="S31" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T31" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W31" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -3776,28 +3803,28 @@
         <v>241</v>
       </c>
       <c r="J32" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="S32" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T32" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W32" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -3817,28 +3844,28 @@
         <v>241</v>
       </c>
       <c r="J33" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M33" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="S33" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="T33" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="W33" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -3858,25 +3885,25 @@
         <v>241</v>
       </c>
       <c r="J34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="S34" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W34" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -3896,25 +3923,25 @@
         <v>241</v>
       </c>
       <c r="J35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M35" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="S35" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W35" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3934,25 +3961,25 @@
         <v>241</v>
       </c>
       <c r="J36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="S36" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W36" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X36">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -3969,25 +3996,25 @@
         <v>185</v>
       </c>
       <c r="J37" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M37" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="S37" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W37" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X37">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -4007,28 +4034,28 @@
         <v>241</v>
       </c>
       <c r="J38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="S38" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="T38" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W38" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -4048,25 +4075,25 @@
         <v>241</v>
       </c>
       <c r="J39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M39" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="S39" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W39" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -4089,28 +4116,28 @@
         <v>187</v>
       </c>
       <c r="J40" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M40" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="S40" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T40" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="W40" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="X40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -4130,28 +4157,28 @@
         <v>241</v>
       </c>
       <c r="J41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="S41" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T41" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="W41" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X41">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -4171,25 +4198,25 @@
         <v>241</v>
       </c>
       <c r="J42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="S42" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W42" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -4215,25 +4242,25 @@
         <v>241</v>
       </c>
       <c r="J43" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="S43" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="W43" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -4259,28 +4286,28 @@
         <v>241</v>
       </c>
       <c r="J44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M44" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="S44" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T44" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="W44" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X44">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -4306,28 +4333,28 @@
         <v>247</v>
       </c>
       <c r="J45" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="S45" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T45" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W45" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X45">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -4347,28 +4374,28 @@
         <v>240</v>
       </c>
       <c r="J46" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M46" t="s">
-        <v>393</v>
+        <v>673</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="S46" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="T46" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="W46" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>41</v>
       </c>
@@ -4385,28 +4412,28 @@
         <v>162</v>
       </c>
       <c r="J47" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="S47" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T47" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="W47" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -4426,25 +4453,25 @@
         <v>241</v>
       </c>
       <c r="J48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M48" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="S48" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="W48" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -4464,28 +4491,28 @@
         <v>241</v>
       </c>
       <c r="J49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M49" t="s">
-        <v>396</v>
+        <v>674</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="S49" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T49" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W49" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -4505,28 +4532,28 @@
         <v>241</v>
       </c>
       <c r="J50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M50" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="S50" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T50" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="W50" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -4546,25 +4573,25 @@
         <v>248</v>
       </c>
       <c r="J51" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="S51" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W51" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -4584,28 +4611,28 @@
         <v>249</v>
       </c>
       <c r="J52" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M52" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="S52" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T52" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="W52" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -4625,25 +4652,25 @@
         <v>249</v>
       </c>
       <c r="J53" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M53" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="S53" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W53" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -4663,25 +4690,25 @@
         <v>241</v>
       </c>
       <c r="J54" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M54" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="S54" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="W54" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -4701,28 +4728,28 @@
         <v>241</v>
       </c>
       <c r="J55" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M55" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="S55" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T55" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W55" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -4742,28 +4769,28 @@
         <v>241</v>
       </c>
       <c r="J56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M56" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="S56" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T56" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W56" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X56">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>49</v>
       </c>
@@ -4783,25 +4810,25 @@
         <v>241</v>
       </c>
       <c r="J57" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M57" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="S57" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W57" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>50</v>
       </c>
@@ -4821,28 +4848,28 @@
         <v>249</v>
       </c>
       <c r="J58" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M58" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="S58" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T58" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="W58" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>50</v>
       </c>
@@ -4862,25 +4889,25 @@
         <v>249</v>
       </c>
       <c r="J59" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M59" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="S59" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W59" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X59">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>51</v>
       </c>
@@ -4900,25 +4927,25 @@
         <v>241</v>
       </c>
       <c r="J60" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M60" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="S60" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W60" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X60">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -4938,28 +4965,28 @@
         <v>250</v>
       </c>
       <c r="J61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M61" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="S61" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T61" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W61" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -4976,25 +5003,25 @@
         <v>182</v>
       </c>
       <c r="J62" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M62" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="S62" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="W62" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X62">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -5014,25 +5041,25 @@
         <v>241</v>
       </c>
       <c r="J63" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M63" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="S63" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="W63" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X63">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -5049,28 +5076,28 @@
         <v>184</v>
       </c>
       <c r="J64" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M64" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="S64" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T64" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="W64" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -5090,28 +5117,28 @@
         <v>249</v>
       </c>
       <c r="J65" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M65" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="S65" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T65" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W65" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -5131,28 +5158,28 @@
         <v>251</v>
       </c>
       <c r="J66" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M66" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="S66" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T66" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W66" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="X66">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>54</v>
       </c>
@@ -5172,28 +5199,28 @@
         <v>241</v>
       </c>
       <c r="J67" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M67" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="S67" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="T67" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W67" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>55</v>
       </c>
@@ -5213,28 +5240,28 @@
         <v>252</v>
       </c>
       <c r="J68" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M68" t="s">
-        <v>415</v>
+        <v>675</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="S68" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="T68" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="W68" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>32</v>
       </c>
@@ -5254,25 +5281,25 @@
         <v>253</v>
       </c>
       <c r="J69" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M69" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="S69" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="W69" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X69">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>56</v>
       </c>
@@ -5292,25 +5319,25 @@
         <v>254</v>
       </c>
       <c r="J70" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M70" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="S70" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="W70" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="X70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -5330,28 +5357,28 @@
         <v>255</v>
       </c>
       <c r="J71" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M71" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="S71" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T71" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="W71" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X71">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>58</v>
       </c>
@@ -5371,25 +5398,25 @@
         <v>239</v>
       </c>
       <c r="J72" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M72" t="s">
-        <v>419</v>
+        <v>676</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="S72" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W72" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>58</v>
       </c>
@@ -5406,25 +5433,25 @@
         <v>206</v>
       </c>
       <c r="J73" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M73" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="S73" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W73" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="X73">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>59</v>
       </c>
@@ -5444,25 +5471,25 @@
         <v>256</v>
       </c>
       <c r="J74" t="s">
-        <v>319</v>
+        <v>684</v>
       </c>
       <c r="M74" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="S74" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W74" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="X74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>60</v>
       </c>
@@ -5482,28 +5509,28 @@
         <v>253</v>
       </c>
       <c r="J75" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M75" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="S75" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T75" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="W75" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X75">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>60</v>
       </c>
@@ -5523,28 +5550,28 @@
         <v>257</v>
       </c>
       <c r="J76" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="M76" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="S76" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T76" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="W76" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X76">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>61</v>
       </c>
@@ -5564,28 +5591,28 @@
         <v>240</v>
       </c>
       <c r="J77" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M77" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="S77" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T77" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="W77" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>62</v>
       </c>
@@ -5605,28 +5632,28 @@
         <v>241</v>
       </c>
       <c r="J78" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M78" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="S78" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T78" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="W78" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X78">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>62</v>
       </c>
@@ -5646,28 +5673,28 @@
         <v>241</v>
       </c>
       <c r="J79" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M79" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="S79" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T79" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="W79" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>63</v>
       </c>
@@ -5687,28 +5714,28 @@
         <v>256</v>
       </c>
       <c r="J80" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="M80" t="s">
-        <v>427</v>
+        <v>677</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="S80" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T80" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="W80" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="X80">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>64</v>
       </c>
@@ -5728,25 +5755,25 @@
         <v>241</v>
       </c>
       <c r="J81" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M81" t="s">
-        <v>428</v>
+        <v>678</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="S81" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="W81" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X81">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>64</v>
       </c>
@@ -5766,25 +5793,25 @@
         <v>258</v>
       </c>
       <c r="J82" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="M82" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="S82" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="W82" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>65</v>
       </c>
@@ -5804,25 +5831,25 @@
         <v>259</v>
       </c>
       <c r="J83" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M83" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="S83" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="W83" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X83">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
@@ -5842,25 +5869,25 @@
         <v>241</v>
       </c>
       <c r="J84" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M84" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="S84" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W84" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X84">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -5880,25 +5907,25 @@
         <v>260</v>
       </c>
       <c r="J85" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M85" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="S85" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W85" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="X85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>67</v>
       </c>
@@ -5918,28 +5945,28 @@
         <v>241</v>
       </c>
       <c r="J86" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M86" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="S86" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T86" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W86" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X86">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>68</v>
       </c>
@@ -5959,25 +5986,25 @@
         <v>261</v>
       </c>
       <c r="J87" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M87" t="s">
-        <v>434</v>
+        <v>679</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="S87" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W87" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="X87">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>69</v>
       </c>
@@ -5997,28 +6024,28 @@
         <v>240</v>
       </c>
       <c r="J88" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M88" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="S88" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T88" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="W88" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>70</v>
       </c>
@@ -6038,28 +6065,28 @@
         <v>241</v>
       </c>
       <c r="J89" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="S89" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T89" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="W89" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="X89">
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>70</v>
       </c>
@@ -6079,28 +6106,28 @@
         <v>241</v>
       </c>
       <c r="J90" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M90" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="S90" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T90" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="W90" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="X90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>27</v>
       </c>
@@ -6120,28 +6147,28 @@
         <v>241</v>
       </c>
       <c r="J91" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="M91" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="S91" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T91" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="W91" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>71</v>
       </c>
@@ -6161,25 +6188,25 @@
         <v>262</v>
       </c>
       <c r="J92" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M92" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="S92" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W92" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X92">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>60</v>
       </c>
@@ -6199,28 +6226,28 @@
         <v>263</v>
       </c>
       <c r="J93" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="M93" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="S93" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T93" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W93" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>72</v>
       </c>
@@ -6240,25 +6267,25 @@
         <v>264</v>
       </c>
       <c r="J94" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M94" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="S94" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W94" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X94">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>27</v>
       </c>
@@ -6278,28 +6305,28 @@
         <v>262</v>
       </c>
       <c r="J95" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="M95" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="S95" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T95" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="W95" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X95">
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>27</v>
       </c>
@@ -6319,28 +6346,28 @@
         <v>241</v>
       </c>
       <c r="J96" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M96" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="S96" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T96" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="W96" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>27</v>
       </c>
@@ -6360,25 +6387,25 @@
         <v>241</v>
       </c>
       <c r="J97" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M97" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="S97" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W97" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X97">
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>27</v>
       </c>
@@ -6398,28 +6425,28 @@
         <v>265</v>
       </c>
       <c r="J98" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="M98" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="S98" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T98" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="W98" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X98">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>27</v>
       </c>
@@ -6439,28 +6466,28 @@
         <v>241</v>
       </c>
       <c r="J99" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M99" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="S99" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T99" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="W99" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X99">
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>73</v>
       </c>
@@ -6480,28 +6507,28 @@
         <v>246</v>
       </c>
       <c r="J100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M100" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="S100" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T100" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="W100" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>73</v>
       </c>
@@ -6521,25 +6548,25 @@
         <v>266</v>
       </c>
       <c r="J101" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="M101" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="S101" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W101" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X101">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>74</v>
       </c>
@@ -6559,28 +6586,28 @@
         <v>241</v>
       </c>
       <c r="J102" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M102" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="S102" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T102" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="W102" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X102">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -6600,28 +6627,28 @@
         <v>267</v>
       </c>
       <c r="J103" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M103" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="S103" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T103" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="W103" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X103">
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>74</v>
       </c>
@@ -6641,28 +6668,28 @@
         <v>246</v>
       </c>
       <c r="J104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M104" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="S104" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T104" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="W104" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X104">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>74</v>
       </c>
@@ -6682,25 +6709,25 @@
         <v>241</v>
       </c>
       <c r="J105" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M105" t="s">
-        <v>452</v>
+        <v>680</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="S105" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="W105" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>74</v>
       </c>
@@ -6720,25 +6747,25 @@
         <v>241</v>
       </c>
       <c r="J106" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M106" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="S106" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="W106" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X106">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>74</v>
       </c>
@@ -6758,28 +6785,28 @@
         <v>268</v>
       </c>
       <c r="J107" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M107" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="N107" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="S107" t="s">
         <v>575</v>
       </c>
-      <c r="S107" t="s">
-        <v>591</v>
-      </c>
       <c r="T107" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="W107" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="X107">
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>75</v>
       </c>
@@ -6799,25 +6826,25 @@
         <v>269</v>
       </c>
       <c r="J108" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="M108" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="S108" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W108" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>76</v>
       </c>
@@ -6837,25 +6864,25 @@
         <v>262</v>
       </c>
       <c r="J109" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M109" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="S109" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="W109" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X109">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>77</v>
       </c>
@@ -6875,25 +6902,25 @@
         <v>266</v>
       </c>
       <c r="J110" t="s">
-        <v>341</v>
+        <v>683</v>
       </c>
       <c r="M110" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="S110" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W110" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X110">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>78</v>
       </c>
@@ -6913,28 +6940,28 @@
         <v>270</v>
       </c>
       <c r="J111" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M111" t="s">
-        <v>458</v>
+        <v>681</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="S111" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T111" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="W111" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="X111">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -6954,25 +6981,25 @@
         <v>253</v>
       </c>
       <c r="J112" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M112" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="S112" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="W112" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X112">
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>79</v>
       </c>
@@ -6992,28 +7019,28 @@
         <v>246</v>
       </c>
       <c r="J113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M113" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="S113" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T113" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="W113" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X113">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>79</v>
       </c>
@@ -7030,28 +7057,28 @@
         <v>232</v>
       </c>
       <c r="J114" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="M114" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="S114" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T114" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="W114" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X114">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>80</v>
       </c>
@@ -7071,28 +7098,28 @@
         <v>253</v>
       </c>
       <c r="J115" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M115" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="S115" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="T115" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="W115" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="X115">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>81</v>
       </c>
@@ -7112,28 +7139,28 @@
         <v>270</v>
       </c>
       <c r="J116" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="M116" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="S116" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T116" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="W116" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="X116">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>81</v>
       </c>
@@ -7153,28 +7180,28 @@
         <v>270</v>
       </c>
       <c r="J117" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M117" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="S117" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T117" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="W117" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="X117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -7191,25 +7218,25 @@
         <v>177</v>
       </c>
       <c r="J118" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M118" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="S118" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W118" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="X118">
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>82</v>
       </c>
@@ -7229,25 +7256,25 @@
         <v>271</v>
       </c>
       <c r="J119" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="M119" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="S119" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="W119" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="X119">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>83</v>
       </c>
@@ -7267,28 +7294,28 @@
         <v>262</v>
       </c>
       <c r="J120" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="M120" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="S120" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="T120" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="W120" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X120">
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>83</v>
       </c>
@@ -7308,25 +7335,25 @@
         <v>272</v>
       </c>
       <c r="J121" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M121" t="s">
-        <v>468</v>
+        <v>682</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="S121" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="W121" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="X121">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -7346,19 +7373,19 @@
         <v>240</v>
       </c>
       <c r="J122" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="M122" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="S122" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="W122" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="X122">
         <v>1</v>
@@ -7366,127 +7393,127 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
-    <hyperlink ref="N110" r:id="rId109"/>
-    <hyperlink ref="N111" r:id="rId110"/>
-    <hyperlink ref="N112" r:id="rId111"/>
-    <hyperlink ref="N113" r:id="rId112"/>
-    <hyperlink ref="N114" r:id="rId113"/>
-    <hyperlink ref="N115" r:id="rId114"/>
-    <hyperlink ref="N116" r:id="rId115"/>
-    <hyperlink ref="N117" r:id="rId116"/>
-    <hyperlink ref="N118" r:id="rId117"/>
-    <hyperlink ref="N119" r:id="rId118"/>
-    <hyperlink ref="N120" r:id="rId119"/>
-    <hyperlink ref="N121" r:id="rId120"/>
-    <hyperlink ref="N122" r:id="rId121"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="N111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="N113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="N117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="N121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E864D799-0169-4BD7-AF12-B20396E76247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="673">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2030,13 +2036,16 @@
   </si>
   <si>
     <t>111 cm</t>
+  </si>
+  <si>
+    <t>Marbre pour la version originale au Louvre. Ici version en bronze.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2081,18 +2090,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2130,7 +2147,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2164,6 +2181,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2198,9 +2216,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2373,11 +2392,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V122"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="18" max="18" width="53.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2445,7 +2467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2477,7 +2499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2515,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2547,7 +2569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2579,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2611,7 +2633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2643,7 +2665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2675,7 +2697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2704,7 +2726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2739,7 +2761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2774,7 +2796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2806,7 +2828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2838,7 +2860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2870,7 +2892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -2902,7 +2924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2940,7 +2962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -2978,7 +3000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -3016,7 +3038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -3048,7 +3070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3086,7 +3108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3124,7 +3146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -3162,7 +3184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3200,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3229,7 +3251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3261,7 +3283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3293,7 +3315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -3322,7 +3344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -3351,7 +3373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -3383,7 +3405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -3415,7 +3437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -3447,7 +3469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -3479,7 +3501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3511,7 +3533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -3540,7 +3562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -3569,7 +3591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -3598,7 +3620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -3627,7 +3649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -3659,7 +3681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -3688,7 +3710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -3717,7 +3739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -3749,7 +3771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3778,7 +3800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -3807,7 +3829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3839,7 +3861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -3871,7 +3893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -3903,7 +3925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -3935,7 +3957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -3964,7 +3986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -3996,7 +4018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -4028,7 +4050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -4057,7 +4079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -4089,7 +4111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -4118,7 +4140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -4147,7 +4169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -4179,7 +4201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -4211,7 +4233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>47</v>
       </c>
@@ -4240,7 +4262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>48</v>
       </c>
@@ -4272,7 +4294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -4301,7 +4323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -4330,7 +4352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -4362,7 +4384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>49</v>
       </c>
@@ -4388,7 +4410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -4417,7 +4439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -4449,7 +4471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -4481,7 +4503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -4513,7 +4535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -4545,7 +4567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -4577,7 +4599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -4606,7 +4628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -4635,7 +4657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -4667,7 +4689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -4696,7 +4718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>56</v>
       </c>
@@ -4725,7 +4747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>57</v>
       </c>
@@ -4754,7 +4776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>58</v>
       </c>
@@ -4786,7 +4808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>58</v>
       </c>
@@ -4818,7 +4840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>59</v>
       </c>
@@ -4850,7 +4872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>60</v>
       </c>
@@ -4882,7 +4904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>60</v>
       </c>
@@ -4914,7 +4936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -4946,7 +4968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -4975,7 +4997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>62</v>
       </c>
@@ -5004,7 +5026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>63</v>
       </c>
@@ -5033,7 +5055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -5062,7 +5084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>64</v>
       </c>
@@ -5091,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>65</v>
       </c>
@@ -5123,7 +5145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -5152,7 +5174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>67</v>
       </c>
@@ -5184,7 +5206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>68</v>
       </c>
@@ -5216,7 +5238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>68</v>
       </c>
@@ -5248,7 +5270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -5280,7 +5302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -5309,7 +5331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:22">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>58</v>
       </c>
@@ -5341,7 +5363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>70</v>
       </c>
@@ -5370,7 +5392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5402,7 +5424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -5434,7 +5456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -5463,7 +5485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -5495,7 +5517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -5527,7 +5549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>71</v>
       </c>
@@ -5559,7 +5581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>71</v>
       </c>
@@ -5588,7 +5610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -5620,7 +5642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -5643,7 +5665,7 @@
         <v>569</v>
       </c>
       <c r="R103" t="s">
-        <v>590</v>
+        <v>672</v>
       </c>
       <c r="S103" t="s">
         <v>651</v>
@@ -5652,7 +5674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>72</v>
       </c>
@@ -5684,7 +5706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -5713,7 +5735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>72</v>
       </c>
@@ -5742,7 +5764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -5774,7 +5796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -5803,7 +5825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>74</v>
       </c>
@@ -5832,7 +5854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -5861,7 +5883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>76</v>
       </c>
@@ -5893,7 +5915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -5922,7 +5944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>77</v>
       </c>
@@ -5954,7 +5976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>77</v>
       </c>
@@ -5986,7 +6008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>78</v>
       </c>
@@ -6018,7 +6040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>79</v>
       </c>
@@ -6050,7 +6072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:22">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>79</v>
       </c>
@@ -6082,7 +6104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:22">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -6108,7 +6130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:22">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>80</v>
       </c>
@@ -6137,7 +6159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:22">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>81</v>
       </c>
@@ -6169,7 +6191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>81</v>
       </c>
@@ -6198,7 +6220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>82</v>
       </c>
@@ -6229,127 +6251,127 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1"/>
-    <hyperlink ref="K3" r:id="rId2"/>
-    <hyperlink ref="K4" r:id="rId3"/>
-    <hyperlink ref="K5" r:id="rId4"/>
-    <hyperlink ref="K6" r:id="rId5"/>
-    <hyperlink ref="K7" r:id="rId6"/>
-    <hyperlink ref="K8" r:id="rId7"/>
-    <hyperlink ref="K9" r:id="rId8"/>
-    <hyperlink ref="K10" r:id="rId9"/>
-    <hyperlink ref="K11" r:id="rId10"/>
-    <hyperlink ref="K12" r:id="rId11"/>
-    <hyperlink ref="K13" r:id="rId12"/>
-    <hyperlink ref="K14" r:id="rId13"/>
-    <hyperlink ref="K15" r:id="rId14"/>
-    <hyperlink ref="K16" r:id="rId15"/>
-    <hyperlink ref="K17" r:id="rId16"/>
-    <hyperlink ref="K18" r:id="rId17"/>
-    <hyperlink ref="K19" r:id="rId18"/>
-    <hyperlink ref="K20" r:id="rId19"/>
-    <hyperlink ref="K21" r:id="rId20"/>
-    <hyperlink ref="K22" r:id="rId21"/>
-    <hyperlink ref="K23" r:id="rId22"/>
-    <hyperlink ref="K24" r:id="rId23"/>
-    <hyperlink ref="K25" r:id="rId24"/>
-    <hyperlink ref="K26" r:id="rId25"/>
-    <hyperlink ref="K27" r:id="rId26"/>
-    <hyperlink ref="K28" r:id="rId27"/>
-    <hyperlink ref="K29" r:id="rId28"/>
-    <hyperlink ref="K30" r:id="rId29"/>
-    <hyperlink ref="K31" r:id="rId30"/>
-    <hyperlink ref="K32" r:id="rId31"/>
-    <hyperlink ref="K33" r:id="rId32"/>
-    <hyperlink ref="K34" r:id="rId33"/>
-    <hyperlink ref="K35" r:id="rId34"/>
-    <hyperlink ref="K36" r:id="rId35"/>
-    <hyperlink ref="K37" r:id="rId36"/>
-    <hyperlink ref="K38" r:id="rId37"/>
-    <hyperlink ref="K39" r:id="rId38"/>
-    <hyperlink ref="K40" r:id="rId39"/>
-    <hyperlink ref="K41" r:id="rId40"/>
-    <hyperlink ref="K42" r:id="rId41"/>
-    <hyperlink ref="K43" r:id="rId42"/>
-    <hyperlink ref="K44" r:id="rId43"/>
-    <hyperlink ref="K45" r:id="rId44"/>
-    <hyperlink ref="K46" r:id="rId45"/>
-    <hyperlink ref="K47" r:id="rId46"/>
-    <hyperlink ref="K48" r:id="rId47"/>
-    <hyperlink ref="K49" r:id="rId48"/>
-    <hyperlink ref="K50" r:id="rId49"/>
-    <hyperlink ref="K51" r:id="rId50"/>
-    <hyperlink ref="K52" r:id="rId51"/>
-    <hyperlink ref="K53" r:id="rId52"/>
-    <hyperlink ref="K54" r:id="rId53"/>
-    <hyperlink ref="K55" r:id="rId54"/>
-    <hyperlink ref="K56" r:id="rId55"/>
-    <hyperlink ref="K57" r:id="rId56"/>
-    <hyperlink ref="K58" r:id="rId57"/>
-    <hyperlink ref="K59" r:id="rId58"/>
-    <hyperlink ref="K60" r:id="rId59"/>
-    <hyperlink ref="K61" r:id="rId60"/>
-    <hyperlink ref="K62" r:id="rId61"/>
-    <hyperlink ref="K63" r:id="rId62"/>
-    <hyperlink ref="K64" r:id="rId63"/>
-    <hyperlink ref="K65" r:id="rId64"/>
-    <hyperlink ref="K66" r:id="rId65"/>
-    <hyperlink ref="K67" r:id="rId66"/>
-    <hyperlink ref="K68" r:id="rId67"/>
-    <hyperlink ref="K69" r:id="rId68"/>
-    <hyperlink ref="K70" r:id="rId69"/>
-    <hyperlink ref="K71" r:id="rId70"/>
-    <hyperlink ref="K72" r:id="rId71"/>
-    <hyperlink ref="K73" r:id="rId72"/>
-    <hyperlink ref="K74" r:id="rId73"/>
-    <hyperlink ref="K75" r:id="rId74"/>
-    <hyperlink ref="K76" r:id="rId75"/>
-    <hyperlink ref="K77" r:id="rId76"/>
-    <hyperlink ref="K78" r:id="rId77"/>
-    <hyperlink ref="K79" r:id="rId78"/>
-    <hyperlink ref="K80" r:id="rId79"/>
-    <hyperlink ref="K81" r:id="rId80"/>
-    <hyperlink ref="K82" r:id="rId81"/>
-    <hyperlink ref="K83" r:id="rId82"/>
-    <hyperlink ref="K84" r:id="rId83"/>
-    <hyperlink ref="K85" r:id="rId84"/>
-    <hyperlink ref="K86" r:id="rId85"/>
-    <hyperlink ref="K87" r:id="rId86"/>
-    <hyperlink ref="K88" r:id="rId87"/>
-    <hyperlink ref="K89" r:id="rId88"/>
-    <hyperlink ref="K90" r:id="rId89"/>
-    <hyperlink ref="K91" r:id="rId90"/>
-    <hyperlink ref="K92" r:id="rId91"/>
-    <hyperlink ref="K93" r:id="rId92"/>
-    <hyperlink ref="K94" r:id="rId93"/>
-    <hyperlink ref="K95" r:id="rId94"/>
-    <hyperlink ref="K96" r:id="rId95"/>
-    <hyperlink ref="K97" r:id="rId96"/>
-    <hyperlink ref="K98" r:id="rId97"/>
-    <hyperlink ref="K99" r:id="rId98"/>
-    <hyperlink ref="K100" r:id="rId99"/>
-    <hyperlink ref="K101" r:id="rId100"/>
-    <hyperlink ref="K102" r:id="rId101"/>
-    <hyperlink ref="K103" r:id="rId102"/>
-    <hyperlink ref="K104" r:id="rId103"/>
-    <hyperlink ref="K105" r:id="rId104"/>
-    <hyperlink ref="K106" r:id="rId105"/>
-    <hyperlink ref="K107" r:id="rId106"/>
-    <hyperlink ref="K108" r:id="rId107"/>
-    <hyperlink ref="K109" r:id="rId108"/>
-    <hyperlink ref="K110" r:id="rId109"/>
-    <hyperlink ref="K111" r:id="rId110"/>
-    <hyperlink ref="K112" r:id="rId111"/>
-    <hyperlink ref="K113" r:id="rId112"/>
-    <hyperlink ref="K114" r:id="rId113"/>
-    <hyperlink ref="K115" r:id="rId114"/>
-    <hyperlink ref="K116" r:id="rId115"/>
-    <hyperlink ref="K117" r:id="rId116"/>
-    <hyperlink ref="K118" r:id="rId117"/>
-    <hyperlink ref="K119" r:id="rId118"/>
-    <hyperlink ref="K120" r:id="rId119"/>
-    <hyperlink ref="K121" r:id="rId120"/>
-    <hyperlink ref="K122" r:id="rId121"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="K23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="K35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="K51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="K63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="K64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="K65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="K66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="K67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="K68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="K69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="K70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="K71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="K72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="K73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="K74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="K75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="K76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="K77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="K78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="K79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="K80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="K81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="K82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="K83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="K84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="K85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="K86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="K87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="K88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="K89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="K90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="K91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="K92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="K93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="K94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="K95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="K96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="K97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="K98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="K99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="K100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="K101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="K102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="K103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="K104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="K105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="K106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="K107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="K108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="K109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="K110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="K111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="K112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="K113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="K114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="K115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="K116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="K117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="K118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="K119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="K120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="K121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="K122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E864D799-0169-4BD7-AF12-B20396E76247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA6421C-ABF8-4E57-968F-F25E089D0F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="676">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1975,9 +1975,6 @@
     <t>270 cm</t>
   </si>
   <si>
-    <t>82 cm environ</t>
-  </si>
-  <si>
     <t>130 cm environ</t>
   </si>
   <si>
@@ -2039,6 +2036,18 @@
   </si>
   <si>
     <t>Marbre pour la version originale au Louvre. Ici version en bronze.</t>
+  </si>
+  <si>
+    <t>Détail extrait du haut -relief "Départ des Volontaires"</t>
+  </si>
+  <si>
+    <t>Haut-relief</t>
+  </si>
+  <si>
+    <t>Façade Est du pied droit Nord de l'Arc de Triomphe</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg/1280px-Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2061,12 +2070,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2085,9 +2100,21 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2393,13 +2420,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V122"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W122"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="10" max="10" width="27.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" style="1"/>
     <col min="18" max="18" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2430,13 +2460,13 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -2466,8 +2496,11 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2486,7 +2519,7 @@
       <c r="I2" t="s">
         <v>349</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>468</v>
       </c>
       <c r="R2" t="s">
@@ -2498,8 +2531,11 @@
       <c r="V2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2518,7 +2554,7 @@
       <c r="I3" t="s">
         <v>350</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>469</v>
       </c>
       <c r="R3" t="s">
@@ -2528,16 +2564,19 @@
         <v>613</v>
       </c>
       <c r="T3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="U3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="V3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -2556,7 +2595,7 @@
       <c r="I4" t="s">
         <v>351</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>470</v>
       </c>
       <c r="R4" t="s">
@@ -2568,8 +2607,11 @@
       <c r="V4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2588,7 +2630,7 @@
       <c r="I5" t="s">
         <v>352</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="2" t="s">
         <v>471</v>
       </c>
       <c r="R5" t="s">
@@ -2598,10 +2640,13 @@
         <v>615</v>
       </c>
       <c r="V5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2620,7 +2665,7 @@
       <c r="I6" t="s">
         <v>353</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="2" t="s">
         <v>472</v>
       </c>
       <c r="R6" t="s">
@@ -2630,10 +2675,13 @@
         <v>616</v>
       </c>
       <c r="V6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2652,7 +2700,7 @@
       <c r="I7" t="s">
         <v>354</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="2" t="s">
         <v>473</v>
       </c>
       <c r="R7" t="s">
@@ -2664,8 +2712,11 @@
       <c r="V7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2681,7 +2732,7 @@
       <c r="I8" t="s">
         <v>355</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="2" t="s">
         <v>474</v>
       </c>
       <c r="R8" t="s">
@@ -2691,13 +2742,16 @@
         <v>617</v>
       </c>
       <c r="T8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="V8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2713,7 +2767,7 @@
       <c r="I9" t="s">
         <v>356</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="2" t="s">
         <v>475</v>
       </c>
       <c r="R9" t="s">
@@ -2725,8 +2779,11 @@
       <c r="V9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2745,7 +2802,7 @@
       <c r="I10" t="s">
         <v>357</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="2" t="s">
         <v>476</v>
       </c>
       <c r="R10" t="s">
@@ -2755,13 +2812,16 @@
         <v>619</v>
       </c>
       <c r="T10" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="V10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2780,7 +2840,7 @@
       <c r="I11" t="s">
         <v>358</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" s="2" t="s">
         <v>477</v>
       </c>
       <c r="R11" t="s">
@@ -2795,8 +2855,11 @@
       <c r="V11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2815,7 +2878,7 @@
       <c r="I12" t="s">
         <v>359</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>478</v>
       </c>
       <c r="R12" t="s">
@@ -2825,10 +2888,13 @@
         <v>621</v>
       </c>
       <c r="V12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2847,7 +2913,7 @@
       <c r="I13" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="2" t="s">
         <v>479</v>
       </c>
       <c r="R13" t="s">
@@ -2859,8 +2925,11 @@
       <c r="V13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -2876,7 +2945,7 @@
       <c r="I14" t="s">
         <v>361</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="2" t="s">
         <v>480</v>
       </c>
       <c r="R14" t="s">
@@ -2886,13 +2955,16 @@
         <v>623</v>
       </c>
       <c r="T14" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="V14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -2911,7 +2983,7 @@
       <c r="I15" t="s">
         <v>362</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="2" t="s">
         <v>481</v>
       </c>
       <c r="R15" t="s">
@@ -2923,8 +2995,11 @@
       <c r="V15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2943,7 +3018,7 @@
       <c r="I16" t="s">
         <v>363</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="2" t="s">
         <v>482</v>
       </c>
       <c r="R16" t="s">
@@ -2953,16 +3028,19 @@
         <v>625</v>
       </c>
       <c r="T16" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U16" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="V16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -2981,7 +3059,7 @@
       <c r="I17" t="s">
         <v>364</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="2" t="s">
         <v>483</v>
       </c>
       <c r="R17" t="s">
@@ -2994,13 +3072,16 @@
         <v>646</v>
       </c>
       <c r="U17" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="V17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -3019,7 +3100,7 @@
       <c r="I18" t="s">
         <v>365</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="2" t="s">
         <v>484</v>
       </c>
       <c r="R18" t="s">
@@ -3029,16 +3110,19 @@
         <v>626</v>
       </c>
       <c r="T18" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="U18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="V18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -3057,7 +3141,7 @@
       <c r="I19" t="s">
         <v>366</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="2" t="s">
         <v>485</v>
       </c>
       <c r="R19" t="s">
@@ -3067,10 +3151,13 @@
         <v>627</v>
       </c>
       <c r="V19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3089,7 +3176,7 @@
       <c r="I20" t="s">
         <v>367</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="2" t="s">
         <v>486</v>
       </c>
       <c r="R20" t="s">
@@ -3099,16 +3186,19 @@
         <v>628</v>
       </c>
       <c r="T20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="U20" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="V20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3127,7 +3217,7 @@
       <c r="I21" t="s">
         <v>367</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="2" t="s">
         <v>487</v>
       </c>
       <c r="R21" t="s">
@@ -3137,16 +3227,19 @@
         <v>629</v>
       </c>
       <c r="T21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U21" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="V21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -3165,7 +3258,7 @@
       <c r="I22" t="s">
         <v>367</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="2" t="s">
         <v>488</v>
       </c>
       <c r="R22" t="s">
@@ -3175,16 +3268,19 @@
         <v>630</v>
       </c>
       <c r="T22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="U22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="V22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3203,7 +3299,7 @@
       <c r="I23" t="s">
         <v>368</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="2" t="s">
         <v>489</v>
       </c>
       <c r="R23" t="s">
@@ -3213,16 +3309,19 @@
         <v>629</v>
       </c>
       <c r="T23" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U23" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="V23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3241,17 +3340,20 @@
       <c r="I24" t="s">
         <v>369</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="2" t="s">
         <v>490</v>
       </c>
       <c r="R24" t="s">
         <v>589</v>
       </c>
       <c r="V24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3270,7 +3372,7 @@
       <c r="I25" t="s">
         <v>370</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="2" t="s">
         <v>491</v>
       </c>
       <c r="R25" t="s">
@@ -3280,10 +3382,13 @@
         <v>631</v>
       </c>
       <c r="V25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3302,7 +3407,7 @@
       <c r="I26" t="s">
         <v>371</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="2" t="s">
         <v>492</v>
       </c>
       <c r="R26" t="s">
@@ -3312,10 +3417,13 @@
         <v>614</v>
       </c>
       <c r="V26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -3334,17 +3442,20 @@
       <c r="I27" t="s">
         <v>372</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="2" t="s">
         <v>493</v>
       </c>
       <c r="R27" t="s">
         <v>597</v>
       </c>
       <c r="V27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -3363,7 +3474,7 @@
       <c r="I28" t="s">
         <v>373</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="2" t="s">
         <v>494</v>
       </c>
       <c r="R28" t="s">
@@ -3372,8 +3483,11 @@
       <c r="V28">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -3392,7 +3506,7 @@
       <c r="I29" t="s">
         <v>374</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" s="2" t="s">
         <v>495</v>
       </c>
       <c r="R29" t="s">
@@ -3404,8 +3518,11 @@
       <c r="V29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -3424,7 +3541,7 @@
       <c r="I30" t="s">
         <v>375</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="2" t="s">
         <v>496</v>
       </c>
       <c r="R30" t="s">
@@ -3434,10 +3551,13 @@
         <v>624</v>
       </c>
       <c r="V30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -3456,7 +3576,7 @@
       <c r="I31" t="s">
         <v>376</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="2" t="s">
         <v>497</v>
       </c>
       <c r="R31" t="s">
@@ -3466,10 +3586,13 @@
         <v>632</v>
       </c>
       <c r="V31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -3488,7 +3611,7 @@
       <c r="I32" t="s">
         <v>377</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="2" t="s">
         <v>498</v>
       </c>
       <c r="R32" t="s">
@@ -3500,8 +3623,11 @@
       <c r="V32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3520,7 +3646,7 @@
       <c r="I33" t="s">
         <v>378</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" s="2" t="s">
         <v>499</v>
       </c>
       <c r="R33" t="s">
@@ -3530,10 +3656,13 @@
         <v>633</v>
       </c>
       <c r="V33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -3552,17 +3681,20 @@
       <c r="I34" t="s">
         <v>379</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="2" t="s">
         <v>500</v>
       </c>
       <c r="R34" t="s">
         <v>589</v>
       </c>
       <c r="V34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W34" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -3581,17 +3713,20 @@
       <c r="I35" t="s">
         <v>380</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="2" t="s">
         <v>501</v>
       </c>
       <c r="R35" t="s">
         <v>590</v>
       </c>
       <c r="V35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -3610,17 +3745,20 @@
       <c r="I36" t="s">
         <v>381</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="2" t="s">
         <v>502</v>
       </c>
       <c r="R36" t="s">
         <v>590</v>
       </c>
       <c r="V36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -3639,17 +3777,20 @@
       <c r="I37" t="s">
         <v>382</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="2" t="s">
         <v>503</v>
       </c>
       <c r="R37" t="s">
         <v>590</v>
       </c>
       <c r="V37">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -3668,7 +3809,7 @@
       <c r="I38" t="s">
         <v>383</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="2" t="s">
         <v>504</v>
       </c>
       <c r="R38" t="s">
@@ -3678,10 +3819,13 @@
         <v>631</v>
       </c>
       <c r="V38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -3700,17 +3844,20 @@
       <c r="I39" t="s">
         <v>384</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="2" t="s">
         <v>505</v>
       </c>
       <c r="R39" t="s">
         <v>589</v>
       </c>
       <c r="V39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -3726,7 +3873,7 @@
       <c r="I40" t="s">
         <v>385</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" s="2" t="s">
         <v>506</v>
       </c>
       <c r="R40" t="s">
@@ -3736,10 +3883,13 @@
         <v>612</v>
       </c>
       <c r="V40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -3758,7 +3908,7 @@
       <c r="I41" t="s">
         <v>386</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" s="2" t="s">
         <v>507</v>
       </c>
       <c r="R41" t="s">
@@ -3768,10 +3918,13 @@
         <v>625</v>
       </c>
       <c r="V41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -3790,17 +3943,20 @@
       <c r="I42" t="s">
         <v>387</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" s="2" t="s">
         <v>508</v>
       </c>
       <c r="R42" t="s">
         <v>589</v>
       </c>
       <c r="V42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -3819,17 +3975,20 @@
       <c r="I43" t="s">
         <v>388</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" s="2" t="s">
         <v>509</v>
       </c>
       <c r="R43" t="s">
         <v>600</v>
       </c>
       <c r="V43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3848,7 +4007,7 @@
       <c r="I44" t="s">
         <v>389</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" s="2" t="s">
         <v>510</v>
       </c>
       <c r="R44" t="s">
@@ -3858,10 +4017,13 @@
         <v>634</v>
       </c>
       <c r="V44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -3880,7 +4042,7 @@
       <c r="I45" t="s">
         <v>390</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" s="2" t="s">
         <v>511</v>
       </c>
       <c r="R45" t="s">
@@ -3890,10 +4052,13 @@
         <v>614</v>
       </c>
       <c r="V45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -3912,7 +4077,7 @@
       <c r="I46" t="s">
         <v>391</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" s="2" t="s">
         <v>512</v>
       </c>
       <c r="R46" t="s">
@@ -3924,8 +4089,11 @@
       <c r="V46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -3944,7 +4112,7 @@
       <c r="I47" t="s">
         <v>392</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" s="2" t="s">
         <v>513</v>
       </c>
       <c r="R47" t="s">
@@ -3954,10 +4122,13 @@
         <v>636</v>
       </c>
       <c r="V47">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W47" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -3976,17 +4147,20 @@
       <c r="I48" t="s">
         <v>393</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" s="2" t="s">
         <v>514</v>
       </c>
       <c r="R48" t="s">
         <v>602</v>
       </c>
       <c r="V48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -4005,7 +4179,7 @@
       <c r="I49" t="s">
         <v>394</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" s="2" t="s">
         <v>515</v>
       </c>
       <c r="R49" t="s">
@@ -4017,8 +4191,11 @@
       <c r="V49">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W49" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -4037,7 +4214,7 @@
       <c r="I50" t="s">
         <v>395</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" s="2" t="s">
         <v>516</v>
       </c>
       <c r="R50" t="s">
@@ -4049,8 +4226,11 @@
       <c r="V50">
         <v>3</v>
       </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -4069,7 +4249,7 @@
       <c r="I51" t="s">
         <v>396</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K51" s="2" t="s">
         <v>517</v>
       </c>
       <c r="R51" t="s">
@@ -4078,8 +4258,11 @@
       <c r="V51">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -4098,7 +4281,7 @@
       <c r="I52" t="s">
         <v>397</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" s="2" t="s">
         <v>518</v>
       </c>
       <c r="R52" t="s">
@@ -4108,10 +4291,13 @@
         <v>638</v>
       </c>
       <c r="V52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W52" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -4130,7 +4316,7 @@
       <c r="I53" t="s">
         <v>398</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K53" s="2" t="s">
         <v>519</v>
       </c>
       <c r="R53" t="s">
@@ -4139,8 +4325,11 @@
       <c r="V53">
         <v>3</v>
       </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -4159,7 +4348,7 @@
       <c r="I54" t="s">
         <v>399</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" s="2" t="s">
         <v>520</v>
       </c>
       <c r="R54" t="s">
@@ -4168,8 +4357,11 @@
       <c r="V54">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -4188,7 +4380,7 @@
       <c r="I55" t="s">
         <v>400</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" s="2" t="s">
         <v>521</v>
       </c>
       <c r="R55" t="s">
@@ -4200,8 +4392,11 @@
       <c r="V55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W55" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -4220,7 +4415,7 @@
       <c r="I56" t="s">
         <v>401</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" s="2" t="s">
         <v>522</v>
       </c>
       <c r="R56" t="s">
@@ -4230,10 +4425,13 @@
         <v>614</v>
       </c>
       <c r="V56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>47</v>
       </c>
@@ -4252,17 +4450,20 @@
       <c r="I57" t="s">
         <v>402</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" s="2" t="s">
         <v>523</v>
       </c>
       <c r="R57" t="s">
         <v>589</v>
       </c>
       <c r="V57">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>48</v>
       </c>
@@ -4281,7 +4482,7 @@
       <c r="I58" t="s">
         <v>403</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" s="2" t="s">
         <v>524</v>
       </c>
       <c r="R58" t="s">
@@ -4291,10 +4492,13 @@
         <v>634</v>
       </c>
       <c r="V58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -4313,7 +4517,7 @@
       <c r="I59" t="s">
         <v>404</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" s="2" t="s">
         <v>525</v>
       </c>
       <c r="R59" t="s">
@@ -4322,8 +4526,11 @@
       <c r="V59">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -4342,17 +4549,20 @@
       <c r="I60" t="s">
         <v>405</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" s="2" t="s">
         <v>526</v>
       </c>
       <c r="R60" t="s">
         <v>589</v>
       </c>
       <c r="V60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>49</v>
       </c>
@@ -4371,7 +4581,7 @@
       <c r="I61" t="s">
         <v>406</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" s="2" t="s">
         <v>527</v>
       </c>
       <c r="R61" t="s">
@@ -4381,10 +4591,13 @@
         <v>632</v>
       </c>
       <c r="V61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W61" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>49</v>
       </c>
@@ -4400,17 +4613,20 @@
       <c r="I62" t="s">
         <v>407</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" s="2" t="s">
         <v>528</v>
       </c>
       <c r="R62" t="s">
         <v>603</v>
       </c>
       <c r="V62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>49</v>
       </c>
@@ -4429,17 +4645,20 @@
       <c r="I63" t="s">
         <v>408</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" s="2" t="s">
         <v>529</v>
       </c>
       <c r="R63" t="s">
         <v>597</v>
       </c>
       <c r="V63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>50</v>
       </c>
@@ -4458,7 +4677,7 @@
       <c r="I64" t="s">
         <v>409</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="2" t="s">
         <v>530</v>
       </c>
       <c r="R64" t="s">
@@ -4470,8 +4689,11 @@
       <c r="V64">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W64" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -4490,7 +4712,7 @@
       <c r="I65" t="s">
         <v>410</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" s="2" t="s">
         <v>531</v>
       </c>
       <c r="R65" t="s">
@@ -4500,10 +4722,13 @@
         <v>631</v>
       </c>
       <c r="V65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W65" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>51</v>
       </c>
@@ -4522,7 +4747,7 @@
       <c r="I66" t="s">
         <v>411</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="2" t="s">
         <v>532</v>
       </c>
       <c r="R66" t="s">
@@ -4534,8 +4759,11 @@
       <c r="V66">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -4554,7 +4782,7 @@
       <c r="I67" t="s">
         <v>412</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="2" t="s">
         <v>533</v>
       </c>
       <c r="R67" t="s">
@@ -4564,10 +4792,13 @@
         <v>632</v>
       </c>
       <c r="V67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -4586,7 +4817,7 @@
       <c r="I68" t="s">
         <v>413</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" s="2" t="s">
         <v>534</v>
       </c>
       <c r="R68" t="s">
@@ -4596,10 +4827,13 @@
         <v>637</v>
       </c>
       <c r="V68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W68" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -4618,7 +4852,7 @@
       <c r="I69" t="s">
         <v>414</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" s="2" t="s">
         <v>535</v>
       </c>
       <c r="R69" t="s">
@@ -4627,8 +4861,11 @@
       <c r="V69">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -4647,17 +4884,20 @@
       <c r="I70" t="s">
         <v>415</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" s="2" t="s">
         <v>536</v>
       </c>
       <c r="R70" t="s">
         <v>602</v>
       </c>
       <c r="V70">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W70" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>55</v>
       </c>
@@ -4676,7 +4916,7 @@
       <c r="I71" t="s">
         <v>416</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K71" s="2" t="s">
         <v>537</v>
       </c>
       <c r="R71" t="s">
@@ -4686,10 +4926,13 @@
         <v>640</v>
       </c>
       <c r="V71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W71" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>56</v>
       </c>
@@ -4708,17 +4951,20 @@
       <c r="I72" t="s">
         <v>417</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" s="2" t="s">
         <v>538</v>
       </c>
       <c r="R72" t="s">
         <v>589</v>
       </c>
       <c r="V72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W72" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>56</v>
       </c>
@@ -4737,7 +4983,7 @@
       <c r="I73" t="s">
         <v>418</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" s="2" t="s">
         <v>539</v>
       </c>
       <c r="R73" t="s">
@@ -4746,8 +4992,11 @@
       <c r="V73">
         <v>3</v>
       </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>57</v>
       </c>
@@ -4766,17 +5015,20 @@
       <c r="I74" t="s">
         <v>419</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K74" s="2" t="s">
         <v>540</v>
       </c>
       <c r="R74" t="s">
         <v>590</v>
       </c>
       <c r="V74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W74" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>58</v>
       </c>
@@ -4795,7 +5047,7 @@
       <c r="I75" t="s">
         <v>420</v>
       </c>
-      <c r="K75" s="1" t="s">
+      <c r="K75" s="2" t="s">
         <v>541</v>
       </c>
       <c r="R75" t="s">
@@ -4805,10 +5057,13 @@
         <v>637</v>
       </c>
       <c r="V75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>58</v>
       </c>
@@ -4827,7 +5082,7 @@
       <c r="I76" t="s">
         <v>421</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" s="2" t="s">
         <v>542</v>
       </c>
       <c r="R76" t="s">
@@ -4839,8 +5094,11 @@
       <c r="V76">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>59</v>
       </c>
@@ -4859,7 +5117,7 @@
       <c r="I77" t="s">
         <v>422</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="K77" s="2" t="s">
         <v>543</v>
       </c>
       <c r="R77" t="s">
@@ -4869,10 +5127,13 @@
         <v>641</v>
       </c>
       <c r="V77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W77" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>60</v>
       </c>
@@ -4891,7 +5152,7 @@
       <c r="I78" t="s">
         <v>423</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="K78" s="2" t="s">
         <v>544</v>
       </c>
       <c r="R78" t="s">
@@ -4903,8 +5164,11 @@
       <c r="V78">
         <v>3</v>
       </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W78" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>60</v>
       </c>
@@ -4923,7 +5187,7 @@
       <c r="I79" t="s">
         <v>424</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K79" s="2" t="s">
         <v>545</v>
       </c>
       <c r="R79" t="s">
@@ -4933,10 +5197,13 @@
         <v>642</v>
       </c>
       <c r="V79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W79" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -4955,7 +5222,7 @@
       <c r="I80" t="s">
         <v>425</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="2" t="s">
         <v>546</v>
       </c>
       <c r="R80" t="s">
@@ -4965,10 +5232,13 @@
         <v>639</v>
       </c>
       <c r="V80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W80" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -4987,7 +5257,7 @@
       <c r="I81" t="s">
         <v>426</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K81" s="2" t="s">
         <v>547</v>
       </c>
       <c r="R81" t="s">
@@ -4996,8 +5266,11 @@
       <c r="V81">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W81" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>62</v>
       </c>
@@ -5016,17 +5289,20 @@
       <c r="I82" t="s">
         <v>427</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" s="2" t="s">
         <v>548</v>
       </c>
       <c r="R82" t="s">
         <v>608</v>
       </c>
       <c r="V82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W82" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>63</v>
       </c>
@@ -5045,7 +5321,7 @@
       <c r="I83" t="s">
         <v>428</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="2" t="s">
         <v>549</v>
       </c>
       <c r="R83" t="s">
@@ -5054,8 +5330,11 @@
       <c r="V83">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W83" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -5074,7 +5353,7 @@
       <c r="I84" t="s">
         <v>429</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" s="2" t="s">
         <v>550</v>
       </c>
       <c r="R84" t="s">
@@ -5083,8 +5362,11 @@
       <c r="V84">
         <v>3</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W84" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>64</v>
       </c>
@@ -5103,17 +5385,20 @@
       <c r="I85" t="s">
         <v>430</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="2" t="s">
         <v>551</v>
       </c>
       <c r="R85" t="s">
         <v>589</v>
       </c>
       <c r="V85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W85" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>65</v>
       </c>
@@ -5132,7 +5417,7 @@
       <c r="I86" t="s">
         <v>431</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="2" t="s">
         <v>552</v>
       </c>
       <c r="R86" t="s">
@@ -5144,8 +5429,11 @@
       <c r="V86">
         <v>3</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W86" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>66</v>
       </c>
@@ -5164,17 +5452,20 @@
       <c r="I87" t="s">
         <v>432</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="2" t="s">
         <v>553</v>
       </c>
       <c r="R87" t="s">
         <v>589</v>
       </c>
       <c r="V87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W87" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>67</v>
       </c>
@@ -5193,7 +5484,7 @@
       <c r="I88" t="s">
         <v>433</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="2" t="s">
         <v>554</v>
       </c>
       <c r="R88" t="s">
@@ -5203,10 +5494,13 @@
         <v>643</v>
       </c>
       <c r="V88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W88" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>68</v>
       </c>
@@ -5225,7 +5519,7 @@
       <c r="I89" t="s">
         <v>434</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K89" s="2" t="s">
         <v>555</v>
       </c>
       <c r="R89" t="s">
@@ -5237,8 +5531,11 @@
       <c r="V89">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W89" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>68</v>
       </c>
@@ -5257,7 +5554,7 @@
       <c r="I90" t="s">
         <v>435</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K90" s="2" t="s">
         <v>556</v>
       </c>
       <c r="R90" t="s">
@@ -5267,10 +5564,13 @@
         <v>645</v>
       </c>
       <c r="V90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="W90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -5289,7 +5589,7 @@
       <c r="I91" t="s">
         <v>436</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="K91" s="2" t="s">
         <v>557</v>
       </c>
       <c r="R91" t="s">
@@ -5299,10 +5599,13 @@
         <v>646</v>
       </c>
       <c r="V91">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W91" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>69</v>
       </c>
@@ -5321,17 +5624,20 @@
       <c r="I92" t="s">
         <v>437</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="2" t="s">
         <v>558</v>
       </c>
       <c r="R92" t="s">
         <v>589</v>
       </c>
       <c r="V92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W92" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>58</v>
       </c>
@@ -5350,7 +5656,7 @@
       <c r="I93" t="s">
         <v>438</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="2" t="s">
         <v>559</v>
       </c>
       <c r="R93" t="s">
@@ -5360,10 +5666,13 @@
         <v>614</v>
       </c>
       <c r="V93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W93" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>70</v>
       </c>
@@ -5382,17 +5691,20 @@
       <c r="I94" t="s">
         <v>439</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="2" t="s">
         <v>560</v>
       </c>
       <c r="R94" t="s">
         <v>589</v>
       </c>
       <c r="V94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W94" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -5411,7 +5723,7 @@
       <c r="I95" t="s">
         <v>440</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="2" t="s">
         <v>561</v>
       </c>
       <c r="R95" t="s">
@@ -5421,10 +5733,13 @@
         <v>647</v>
       </c>
       <c r="V95">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W95" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -5443,7 +5758,7 @@
       <c r="I96" t="s">
         <v>441</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="K96" s="2" t="s">
         <v>562</v>
       </c>
       <c r="R96" t="s">
@@ -5455,8 +5770,11 @@
       <c r="V96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W96" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -5475,17 +5793,20 @@
       <c r="I97" t="s">
         <v>442</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="K97" s="2" t="s">
         <v>563</v>
       </c>
       <c r="R97" t="s">
         <v>590</v>
       </c>
       <c r="V97">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W97" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -5504,7 +5825,7 @@
       <c r="I98" t="s">
         <v>443</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K98" s="2" t="s">
         <v>564</v>
       </c>
       <c r="R98" t="s">
@@ -5514,10 +5835,13 @@
         <v>649</v>
       </c>
       <c r="V98">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W98" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -5536,7 +5860,7 @@
       <c r="I99" t="s">
         <v>444</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K99" s="2" t="s">
         <v>565</v>
       </c>
       <c r="R99" t="s">
@@ -5546,10 +5870,13 @@
         <v>650</v>
       </c>
       <c r="V99">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W99" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>71</v>
       </c>
@@ -5568,7 +5895,7 @@
       <c r="I100" t="s">
         <v>445</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K100" s="2" t="s">
         <v>566</v>
       </c>
       <c r="R100" t="s">
@@ -5578,10 +5905,13 @@
         <v>640</v>
       </c>
       <c r="V100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W100" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>71</v>
       </c>
@@ -5600,7 +5930,7 @@
       <c r="I101" t="s">
         <v>446</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K101" s="2" t="s">
         <v>567</v>
       </c>
       <c r="R101" t="s">
@@ -5609,8 +5939,11 @@
       <c r="V101">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W101" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>72</v>
       </c>
@@ -5629,52 +5962,72 @@
       <c r="I102" t="s">
         <v>447</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="2" t="s">
         <v>568</v>
       </c>
       <c r="R102" t="s">
-        <v>589</v>
-      </c>
-      <c r="S102" t="s">
-        <v>614</v>
+        <v>590</v>
+      </c>
+      <c r="S102">
+        <v>96</v>
+      </c>
+      <c r="T102">
+        <v>75</v>
+      </c>
+      <c r="U102">
+        <v>50</v>
       </c>
       <c r="V102">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+        <v>1</v>
+      </c>
+      <c r="W102" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I103" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K103" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="R103" t="s">
-        <v>672</v>
-      </c>
-      <c r="S103" t="s">
-        <v>651</v>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="R103" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="S103" s="3">
+        <v>82</v>
+      </c>
+      <c r="T103" s="3">
+        <v>88</v>
+      </c>
+      <c r="U103" s="3">
+        <v>48</v>
       </c>
       <c r="V103">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W103" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>72</v>
       </c>
@@ -5693,20 +6046,35 @@
       <c r="I104" t="s">
         <v>449</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" s="2" t="s">
         <v>570</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>571</v>
       </c>
       <c r="R104" t="s">
         <v>589</v>
       </c>
-      <c r="S104" t="s">
-        <v>646</v>
+      <c r="S104">
+        <v>63</v>
+      </c>
+      <c r="T104">
+        <v>32</v>
+      </c>
+      <c r="U104">
+        <v>32</v>
       </c>
       <c r="V104">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W104" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -5725,17 +6093,38 @@
       <c r="I105" t="s">
         <v>450</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K105" s="2" t="s">
         <v>571</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>673</v>
       </c>
       <c r="R105" t="s">
         <v>600</v>
       </c>
+      <c r="S105">
+        <v>1160</v>
+      </c>
+      <c r="T105">
+        <v>600</v>
+      </c>
+      <c r="U105">
+        <v>263</v>
+      </c>
       <c r="V105">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W105" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>72</v>
       </c>
@@ -5754,17 +6143,26 @@
       <c r="I106" t="s">
         <v>451</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K106" s="2" t="s">
         <v>572</v>
       </c>
       <c r="R106" t="s">
         <v>600</v>
       </c>
+      <c r="S106">
+        <v>315</v>
+      </c>
+      <c r="T106">
+        <v>175</v>
+      </c>
       <c r="V106">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W106" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -5783,20 +6181,29 @@
       <c r="I107" t="s">
         <v>452</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="K107" s="2" t="s">
         <v>573</v>
       </c>
       <c r="R107" t="s">
         <v>589</v>
       </c>
-      <c r="S107" t="s">
-        <v>634</v>
+      <c r="S107">
+        <v>215</v>
+      </c>
+      <c r="T107">
+        <v>195</v>
+      </c>
+      <c r="U107">
+        <v>96</v>
       </c>
       <c r="V107">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="W107" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -5815,17 +6222,20 @@
       <c r="I108" t="s">
         <v>453</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="K108" s="2" t="s">
         <v>574</v>
       </c>
       <c r="R108" t="s">
         <v>589</v>
       </c>
       <c r="V108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W108" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>74</v>
       </c>
@@ -5844,7 +6254,7 @@
       <c r="I109" t="s">
         <v>454</v>
       </c>
-      <c r="K109" s="1" t="s">
+      <c r="K109" s="2" t="s">
         <v>575</v>
       </c>
       <c r="R109" t="s">
@@ -5853,8 +6263,11 @@
       <c r="V109">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W109" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>75</v>
       </c>
@@ -5873,17 +6286,20 @@
       <c r="I110" t="s">
         <v>455</v>
       </c>
-      <c r="K110" s="1" t="s">
+      <c r="K110" s="2" t="s">
         <v>576</v>
       </c>
       <c r="R110" t="s">
         <v>589</v>
       </c>
       <c r="V110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W110" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>76</v>
       </c>
@@ -5902,20 +6318,23 @@
       <c r="I111" t="s">
         <v>456</v>
       </c>
-      <c r="K111" s="1" t="s">
+      <c r="K111" s="2" t="s">
         <v>577</v>
       </c>
       <c r="R111" t="s">
         <v>590</v>
       </c>
       <c r="S111" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="V111">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -5934,7 +6353,7 @@
       <c r="I112" t="s">
         <v>457</v>
       </c>
-      <c r="K112" s="1" t="s">
+      <c r="K112" s="2" t="s">
         <v>578</v>
       </c>
       <c r="R112" t="s">
@@ -5943,8 +6362,11 @@
       <c r="V112">
         <v>3</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W112" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>77</v>
       </c>
@@ -5963,7 +6385,7 @@
       <c r="I113" t="s">
         <v>458</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="K113" s="2" t="s">
         <v>579</v>
       </c>
       <c r="R113" t="s">
@@ -5973,10 +6395,13 @@
         <v>641</v>
       </c>
       <c r="V113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>77</v>
       </c>
@@ -5995,20 +6420,23 @@
       <c r="I114" t="s">
         <v>459</v>
       </c>
-      <c r="K114" s="1" t="s">
+      <c r="K114" s="2" t="s">
         <v>580</v>
       </c>
       <c r="R114" t="s">
         <v>590</v>
       </c>
       <c r="S114" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="V114">
         <v>3</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W114" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>78</v>
       </c>
@@ -6027,7 +6455,7 @@
       <c r="I115" t="s">
         <v>460</v>
       </c>
-      <c r="K115" s="1" t="s">
+      <c r="K115" s="2" t="s">
         <v>581</v>
       </c>
       <c r="R115" t="s">
@@ -6037,10 +6465,13 @@
         <v>639</v>
       </c>
       <c r="V115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W115" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>79</v>
       </c>
@@ -6059,20 +6490,23 @@
       <c r="I116" t="s">
         <v>461</v>
       </c>
-      <c r="K116" s="1" t="s">
+      <c r="K116" s="2" t="s">
         <v>582</v>
       </c>
       <c r="R116" t="s">
         <v>590</v>
       </c>
       <c r="S116" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="V116">
         <v>3</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>79</v>
       </c>
@@ -6091,20 +6525,23 @@
       <c r="I117" t="s">
         <v>462</v>
       </c>
-      <c r="K117" s="1" t="s">
+      <c r="K117" s="2" t="s">
         <v>583</v>
       </c>
       <c r="R117" t="s">
         <v>590</v>
       </c>
       <c r="S117" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="V117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W117" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>51</v>
       </c>
@@ -6120,7 +6557,7 @@
       <c r="I118" t="s">
         <v>463</v>
       </c>
-      <c r="K118" s="1" t="s">
+      <c r="K118" s="2" t="s">
         <v>584</v>
       </c>
       <c r="R118" t="s">
@@ -6129,8 +6566,11 @@
       <c r="V118">
         <v>3</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W118" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>80</v>
       </c>
@@ -6149,17 +6589,20 @@
       <c r="I119" t="s">
         <v>464</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="K119" s="2" t="s">
         <v>585</v>
       </c>
       <c r="R119" t="s">
         <v>589</v>
       </c>
       <c r="V119">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W119" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>81</v>
       </c>
@@ -6178,7 +6621,7 @@
       <c r="I120" t="s">
         <v>465</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="K120" s="2" t="s">
         <v>586</v>
       </c>
       <c r="R120" t="s">
@@ -6190,8 +6633,11 @@
       <c r="V120">
         <v>3</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W120" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>81</v>
       </c>
@@ -6210,17 +6656,20 @@
       <c r="I121" t="s">
         <v>466</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" s="2" t="s">
         <v>587</v>
       </c>
       <c r="R121" t="s">
         <v>611</v>
       </c>
       <c r="V121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="W121" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>82</v>
       </c>
@@ -6239,14 +6688,17 @@
       <c r="I122" t="s">
         <v>467</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="K122" s="2" t="s">
         <v>588</v>
       </c>
       <c r="R122" t="s">
         <v>590</v>
       </c>
       <c r="V122">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="W122" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -6372,6 +6824,8 @@
     <hyperlink ref="K120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
     <hyperlink ref="K121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
     <hyperlink ref="K122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="M104" r:id="rId122" display="https://upload.wikimedia.org/wikipedia/commons/thumb/8/83/Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg/960px-Le_D%C3%A9part_des_Volontaires_%28La_Marseillaise%29_par_Rude%2C_Arc_de_Triomphe_Etoile_Paris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E0B94170-4A14-4967-97FB-7D2B73DCDC52}"/>
+    <hyperlink ref="M105" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a5/Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg/1280px-Front_left_views_of_the_Arc_de_Triomphe%2C_Paris_21_October_2010.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0CDB5CDC-9D89-47BE-A507-C580E839527D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC923CD-AB62-4C55-B543-4AE2A01FE005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083AD3FA-043A-4238-AEF3-767393AE8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="684">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2069,6 +2069,9 @@
   </si>
   <si>
     <t>190 (statue) 130 (socle)</t>
+  </si>
+  <si>
+    <t>Monument</t>
   </si>
 </sst>
 </file>
@@ -7514,7 +7517,7 @@
         <v>650</v>
       </c>
       <c r="Q121" t="s">
-        <v>657</v>
+        <v>683</v>
       </c>
       <c r="R121" t="s">
         <v>651</v>

--- a/quizzes/sculpture-19e.xlsx
+++ b/quizzes/sculpture-19e.xlsx
@@ -7536,7 +7536,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Architecture </t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
